--- a/docs/xlsx/jobs-2026-08-25.xlsx
+++ b/docs/xlsx/jobs-2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1009">
   <si>
     <t>Title</t>
   </si>
@@ -130,6 +130,9 @@
     <t>general-stewardship</t>
   </si>
   <si>
+    <t>NAFSN</t>
+  </si>
+  <si>
     <t>https://www.conservationjobboard.com/job-listing-buildings-and-grounds-technician-west-st-paul-minnesota/5835023575</t>
   </si>
   <si>
@@ -565,6 +568,99 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-management-specialist-russell--riverton-iowa/4150051360</t>
   </si>
   <si>
+    <t>Data and Analytics Director (1-year Term)</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/data-and-analytics-director-1-year-term/</t>
+  </si>
+  <si>
+    <t>Senior Forest Ecologist</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Ecology</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-forest-ecologist/</t>
+  </si>
+  <si>
+    <t>Senior Workplace Support Specialist (2-Year Term)</t>
+  </si>
+  <si>
+    <t>Denver, Colorado, United States</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-workplace-support-specialist-2-year-term/</t>
+  </si>
+  <si>
+    <t>Accountant | Remote in the United States (Central or Eastern Time Zones Only)</t>
+  </si>
+  <si>
+    <t>Cultural Survival</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cf4dd8a43a64518ae976472ea6bc4c3-accountant-remote-in-the-united-states-central-or-eastern-time-zones-only-cultural-survival-cambridge</t>
+  </si>
+  <si>
+    <t>Activity Specialist</t>
+  </si>
+  <si>
+    <t>Partnership with Children</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b199b995ef3040388a5777a5f0850ed4-activity-specialist-partnership-with-children-kings-county</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80bf05f6890748988ad4e9734b8f008f-activity-specialist-partnership-with-children-bronx-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/207842d5b020402483a9f3731c6f908c-activity-specialist-partnership-with-children-kings-county</t>
+  </si>
+  <si>
     <t>Administrative Assistant</t>
   </si>
   <si>
@@ -574,9 +670,6 @@
     <t>Hamden, Connecticut</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 20.00 - 25.00/hour</t>
   </si>
   <si>
@@ -586,15 +679,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/6b11fff707c04edc89c4c9d89a4d330b-administrative-assistant-congregation-mishkan-israel-hamden</t>
   </si>
   <si>
+    <t>Huru International</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Poverty, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/559afd08a2294491a7a0deeef59030bd-administrative-assistant-huru-international-new-york</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator, Community Services Team</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 28.58 - 30.08/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/754831daf06446938ad9c8a028149847-administrative-coordinator-community-services-team-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
     <t>Administrative Project Manager (Contract Based)</t>
   </si>
   <si>
     <t>Field Impact Partners</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Contract</t>
   </si>
   <si>
@@ -607,6 +730,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/a2f2e1571d6e46fa8c0017393bdf0e55-administrative-project-manager-contract-based-field-impact-partners-seattle</t>
   </si>
   <si>
+    <t>Advancement Director, Great Lakes Chapter</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Ohio)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32a4d8930c68441d89f241c204cbabad-advancement-director-great-lakes-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>After School Chess Instructor</t>
+  </si>
+  <si>
+    <t>Vision Ed Inc.</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfba6acfc9fb40f6b2c32f6e2928013f-after-school-chess-instructor-vision-ed-inc-kings-county</t>
+  </si>
+  <si>
     <t>Agroflorestor(a)</t>
   </si>
   <si>
@@ -625,12 +784,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/a0903835ca494a559605c5fa82464005-agroflorestora-eco-caminhos-nova-friburgo</t>
   </si>
   <si>
+    <t>Analyst / Sr. Analyst</t>
+  </si>
+  <si>
+    <t>Public Equity Group</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/b76f3f28f3a04bff92c39de22fc5f64a-analyst-sr-analyst-public-equity-group-newburgh</t>
+  </si>
+  <si>
+    <t>Arizona Organizer</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13e8d9208bda43579bd39d4269a9ed02-arizona-organizer-reproductive-freedom-for-all-phoenix</t>
+  </si>
+  <si>
     <t>Staatsburg, New York</t>
   </si>
   <si>
-    <t>USD 55000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Environment, Science Technology, Water Sanitation</t>
   </si>
   <si>
@@ -652,12 +841,27 @@
     <t>INR 700000.00 - 900000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/696c958be5184ff081597ef6635bf775-assistant-manager-finance-mumbai-ground-zero-mumbai</t>
   </si>
   <si>
+    <t>Associate Director</t>
+  </si>
+  <si>
+    <t>Amirah, Inc.</t>
+  </si>
+  <si>
+    <t>Beverly, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e40dba60fbf245b39dbddded866db564-associate-director-amirah-inc-beverly</t>
+  </si>
+  <si>
     <t>Associate Director for Events</t>
   </si>
   <si>
@@ -676,12 +880,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/caf31189d2b04fdc8de40dee238d939b-associate-director-for-events-american-flood-coalition-washington</t>
   </si>
   <si>
+    <t>Association Data Manager</t>
+  </si>
+  <si>
+    <t>US Composting Council</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9870dfc180254976ba9e67aab3278e71-association-data-manager-us-composting-council-raleigh</t>
+  </si>
+  <si>
+    <t>Attorney: Civil Litigation, Judgment Enforcement (3905)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/7f3bbd91a2e54e3e840404315115fa4b-attorney-civil-litigation-judgment-enforcement-3905-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
     <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d4ad20739f914117bb80ec968589ede1-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fb235e23bd6415ba4264c3b4224b4b5-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
     <t>Bilingual Community Outreach Specialist (Spanish/English)</t>
   </si>
   <si>
@@ -700,6 +937,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e3eae630213344bab3ef9f30e1d3f0a2-bilingual-community-outreach-specialist-spanishenglish-pennsylvania-health-access-network-stroudsburg</t>
   </si>
   <si>
+    <t>Bilingual Social Worker/Therapist</t>
+  </si>
+  <si>
+    <t>The New York Center for Children</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48733aa29b2b4c55830e8f176f2ed0cf-bilingual-social-workertherapist-the-new-york-center-for-children-new-york</t>
+  </si>
+  <si>
     <t>Board Relations Manager &amp; Executive Assistant to the CEO</t>
   </si>
   <si>
@@ -718,6 +970,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/52e7e3e4bdc9459d8ab13ee19f8b0da1-board-relations-manager-executive-assistant-to-the-ceo-public-justice-foundation-washington</t>
   </si>
   <si>
+    <t>Case Manager (Supported Living Disability Services)</t>
+  </si>
+  <si>
+    <t>Toolworks</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 73819.00 - 75592.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e0f5bd7cf224221b452a65a12971276-case-manager-supported-living-disability-services-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Chief Development &amp; Communications Officer</t>
+  </si>
+  <si>
+    <t>ica.fund</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d4bed0a34574907ba58de960aba7f9f-chief-development-communications-officer-icafund-oakland</t>
+  </si>
+  <si>
     <t>Children's Teacher</t>
   </si>
   <si>
@@ -736,6 +1021,90 @@
     <t>https://www.idealist.org/en/nonprofit-job/10cf70b654da4070ae6a538d642ef1ae-childrens-teacher-together-for-youth-canaan</t>
   </si>
   <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Maine</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 65650.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d91dc39610ed4034a31ecf1dc87fb7cb-communications-associate-american-civil-liberties-union-of-maine-portland</t>
+  </si>
+  <si>
+    <t>Communications Coordinator</t>
+  </si>
+  <si>
+    <t>National Youth Employment Coalition</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f589a5cca024eb39a8425b3232ece70-communications-coordinator-national-youth-employment-coalition-washington</t>
+  </si>
+  <si>
+    <t>Community Canvasser</t>
+  </si>
+  <si>
+    <t>New Yorkers United for Child Care</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa9fd1db903341c39fe9d21e7802a462-community-canvasser-new-yorkers-united-for-child-care-new-york</t>
+  </si>
+  <si>
+    <t>Community Development Partnerships Manager</t>
+  </si>
+  <si>
+    <t>Homestead Community Land Trust</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c9c742a27c8400e94afcb4564d8252f-community-development-partnerships-manager-homestead-community-land-trust-seattle</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Project Citizenship</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bce2b1a49d8444a1b77cd213bf05a51a-community-engagement-manager-project-citizenship-boston</t>
+  </si>
+  <si>
     <t>Community Outreach Specialist</t>
   </si>
   <si>
@@ -748,6 +1117,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/93fc2674940f4c4e81644e819a2ce823-community-outreach-specialist-pennsylvania-health-access-network-stroudsburg</t>
   </si>
   <si>
+    <t>Consultant, Health Equity Data &amp; Evaluation</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>USD 87360.00 - 120640.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/cc70e145c0e049b3845f6cb5ba86f0f7-consultant-health-equity-data-evaluation-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Coordinator Farmers Market Recovery</t>
+  </si>
+  <si>
+    <t>Food Forward</t>
+  </si>
+  <si>
+    <t>Ventura, California</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 24.04/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce6ddb3e496648db854436e570eea3b8-coordinator-farmers-market-recovery-food-forward-ventura</t>
+  </si>
+  <si>
+    <t>Data and Analytics Director (1-year term)</t>
+  </si>
+  <si>
+    <t>USD 112000.00 - 131000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7cc4fb39d2584a40b64478fc4f1c2618-data-and-analytics-director-1-year-term-the-wilderness-society-washington</t>
+  </si>
+  <si>
     <t>Data Engineer</t>
   </si>
   <si>
@@ -763,6 +1177,150 @@
     <t>https://www.idealist.org/en/nonprofit-job/52c25ba1b3fb4f3580d2f43b1213955a-data-engineer-nami-national-alliance-on-mental-illness-arlington</t>
   </si>
   <si>
+    <t>Data Manager</t>
+  </si>
+  <si>
+    <t>NYC Independent Budget Office</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/5aa0855154274405b965892030bf4ca6-data-manager-nyc-independent-budget-office-new-york</t>
+  </si>
+  <si>
+    <t>DC/MD/VA Chapter Director</t>
+  </si>
+  <si>
+    <t>African Communities Together</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f810a634800144eb9aac8a174a7609bf-dcmdva-chapter-director-african-communities-together-washington</t>
+  </si>
+  <si>
+    <t>DC/MD/VA Community Organizer</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b26c2303ea1f4066bab1164f732fc4d9-dcmdva-community-organizer-african-communities-together-washington</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Loudoun Hunger Relief</t>
+  </si>
+  <si>
+    <t>Leesburg, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3d6d3282934472084766293fb5a860b-development-coordinator-loudoun-hunger-relief-leesburg</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Birch Community Services Inc.</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78de382259374298a63369a995726ac3-development-manager-birch-community-services-inc-portland</t>
+  </si>
+  <si>
+    <t>Baltimore's Promise</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54a5daf8337f4ab78574ac33b2b72c68-development-manager-baltimores-promise-baltimore</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>Congregation Beit Simchat Torah</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ba3d6da418a462986434ca03c1f2cd4-director-of-advancement-congregation-beit-simchat-torah-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Citizens Committee for New York City</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d22d5486fcd431899a0bae47e564c56-director-of-communications-citizens-committee-for-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Director of Community Services</t>
+  </si>
+  <si>
+    <t>Real Escape from the Sex Trade (REST)</t>
+  </si>
+  <si>
+    <t>USD 118000.00 - 128000.00/year</t>
+  </si>
+  <si>
+    <t>Victim Support, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdd39bc5fc0e42d3bb6e2e06f70d8b8e-director-of-community-services-real-escape-from-the-sex-trade-rest-seattle</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Merit America</t>
+  </si>
+  <si>
+    <t>USD 148000.00 - 148000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22c3e32f4c634d08b9a7fcdac087dd4f-director-of-development-merit-america-washington</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -778,15 +1336,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/3493326f76494b54915164df13b1aa6a-director-of-finance-trust-neighborhoods-kansas-city</t>
   </si>
   <si>
+    <t>Director of Global IT</t>
+  </si>
+  <si>
+    <t>Somatic Experiencing International</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cbb86fec7a242cba1d6b1294e2558db-director-of-global-it-somatic-experiencing-international-boulder</t>
+  </si>
+  <si>
+    <t>Director of Major Gifts and Leadership Giving</t>
+  </si>
+  <si>
+    <t>Issue One</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b852bc06f3bf4813922b8c1c62bf5db6-director-of-major-gifts-and-leadership-giving-issue-one-washington</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Hispanic Federation</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be2c7269080c4fa2bff6d40a64462d09-director-of-operations-hispanic-federation-charlotte</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>My Friend's Place</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5915b6e8ba641cf8e9113d8ed1bafaa-director-of-programs-my-friends-place-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Programs &amp; Operations</t>
+  </si>
+  <si>
+    <t>Neighborhood Housing Services of the Inland Empire</t>
+  </si>
+  <si>
+    <t>San Bernardino, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Race Ethnicity, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/23d1a1aa3c2143eaa2735fd6e73e62d6-director-of-programs-operations-neighborhood-housing-services-of-the-inland-empire-san-bernardino</t>
+  </si>
+  <si>
+    <t>Director Position for La Comunidad que Construimos (NGO)</t>
+  </si>
+  <si>
+    <t>La Comunidad que Construimos - LCQC Peru</t>
+  </si>
+  <si>
+    <t>Trujillo, La Libertad, PE</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2eaa47fc1ea49abb0ff11d10a979fc0-director-position-for-la-comunidad-que-construimos-ngo-la-comunidad-que-construimos-lcqc-peru-trujillo</t>
+  </si>
+  <si>
     <t>Director, Business Intelligence and Analytics</t>
   </si>
   <si>
     <t>UJA-Federation of New York</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 150000.00 - 160000.00/year</t>
   </si>
   <si>
@@ -796,6 +1441,141 @@
     <t>https://www.idealist.org/en/nonprofit-job/7c0ba0708a4a4b59b41c86d1c0ee4515-director-business-intelligence-and-analytics-uja-federation-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Director, Development Operations</t>
+  </si>
+  <si>
+    <t>Brady United Against Gun Violence</t>
+  </si>
+  <si>
+    <t>USD 112000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1411bc5a3e0c435cbff204c0517d86b3-director-development-operations-brady-united-against-gun-violence-washington</t>
+  </si>
+  <si>
+    <t>Director, District Partnerships &amp; Growth</t>
+  </si>
+  <si>
+    <t>New Tech Network</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/471812e31bf349b4872704a8587db0fc-director-district-partnerships-growth-new-tech-network-napa</t>
+  </si>
+  <si>
+    <t>Donor Relations Coordinator</t>
+  </si>
+  <si>
+    <t>Friends for Life</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23ed8ddde61846208ac8741a5598b753-donor-relations-coordinator-friends-for-life-houston</t>
+  </si>
+  <si>
+    <t>Donor Relations Officer</t>
+  </si>
+  <si>
+    <t>Center for Constitutional Rights</t>
+  </si>
+  <si>
+    <t>USD 98198.00 - 119254.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e2de5963b3f4835927672645e130fc5-donor-relations-officer-center-for-constitutional-rights-new-york</t>
+  </si>
+  <si>
+    <t>DSP Supported and Independent Living Instructor</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3eda0ddd51ff42d6a94f16d8c4cb4f54-dsp-supported-and-independent-living-instructor-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>DSP Supported and Independent Living Lead</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0694e7c7721a4460b63a8f8a8cd87ae4-dsp-supported-and-independent-living-lead-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Economic Development Data &amp; Program Manager</t>
+  </si>
+  <si>
+    <t>Alliance for Downtown New York, Inc.</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a789aa8918014704936dad653399da48-economic-development-data-program-manager-alliance-for-downtown-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Employment Specialist</t>
+  </si>
+  <si>
+    <t>CARES of Washington</t>
+  </si>
+  <si>
+    <t>Tacoma, Washington</t>
+  </si>
+  <si>
+    <t>Disability, Job Workplace, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d0e7da579c14609829d194192e6c88c-employment-specialist-cares-of-washington-tacoma</t>
+  </si>
+  <si>
+    <t>The American Revolution Institute of the Society of the Cincinnati</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/706c4b192a0b4459b2769d237e9b0ec8-executive-assistant-the-american-revolution-institute-of-the-society-of-the-cincinnati-washington</t>
+  </si>
+  <si>
+    <t>Identity, Inc.</t>
+  </si>
+  <si>
+    <t>Gaithersburg, Maryland</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ec951e630e644cf9c660cbc6c139c37-executive-assistant-identity-inc-gaithersburg</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -814,6 +1594,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/03c6bdd681ba4fc598ab834d69ed6b08-executive-director-voices-jackson-hole-jackson</t>
   </si>
   <si>
+    <t>Insperity-Client</t>
+  </si>
+  <si>
+    <t>Women, Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/43a084a3f7dc43879015471b16344e25-executive-director-insperity-client-houston</t>
+  </si>
+  <si>
+    <t>American Geographical Society</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9eeedcccb09449bb81a1c95fdd73184a-executive-director-american-geographical-society-new-york</t>
+  </si>
+  <si>
     <t>EXECUTIVE DIRECTOR</t>
   </si>
   <si>
@@ -823,18 +1624,102 @@
     <t>Morristown, New Jersey</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
-    <t>USD 65000.00 - 75000.00/year</t>
-  </si>
-  <si>
     <t>Education, Communications Access, Immigrants Or Refugees</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/bb146f4822e947319bad92158c637b58-executive-director-literacy-volunteers-of-morris-county-inc-morristown</t>
   </si>
   <si>
+    <t>Executive Director, Elohee Retreat Center</t>
+  </si>
+  <si>
+    <t>Elohee Retreat Center</t>
+  </si>
+  <si>
+    <t>Sautee Nacoochee, Georgia</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/75f81e6cc7e8463dac824551f46c689e-executive-director-elohee-retreat-center-elohee-retreat-center-sautee-nacoochee</t>
+  </si>
+  <si>
+    <t>Family Closet &amp; Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Chosen, Inc. of Wisconsin</t>
+  </si>
+  <si>
+    <t>Waukesha, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b494c1c315344e73a6f92a2febb30b0c-family-closet-volunteer-coordinator-chosen-inc-of-wisconsin-waukesha</t>
+  </si>
+  <si>
+    <t>Finance and Operations Assistant</t>
+  </si>
+  <si>
+    <t>WOMEN'S WAY</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1106ee1109ba496aa15a64ae5034b41e-finance-and-operations-assistant-womens-way-philadelphia</t>
+  </si>
+  <si>
+    <t>Finance and Operations Manager</t>
+  </si>
+  <si>
+    <t>Ventura Land Trust</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/864056e19cba4fa3a05d9c968309c27e-finance-and-operations-manager-ventura-land-trust-ventura</t>
+  </si>
+  <si>
+    <t>Finance Director/Controller</t>
+  </si>
+  <si>
+    <t>Urban Alliance</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0dadee29b0848299c00832e2ddf901a-finance-directorcontroller-urban-alliance-washington</t>
+  </si>
+  <si>
+    <t>GALLERY DIRECTOR, CURATOR OF EXHIBITIONS &amp; PROGRAM</t>
+  </si>
+  <si>
+    <t>Art Students League of New York</t>
+  </si>
+  <si>
+    <t>USD 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b68c3261c3314e7d851b89bc111515e3-gallery-director-curator-of-exhibitions-program-art-students-league-of-new-york-new-york</t>
+  </si>
+  <si>
     <t>Grants and Communications Manager</t>
   </si>
   <si>
@@ -853,6 +1738,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5703a155e4ca466f941b341affa62643-grants-and-communications-manager-rialto-center-for-creativity-westfield</t>
   </si>
   <si>
+    <t>Group Leader</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef2e99a963554f238aa3077f49379023-group-leader-partnership-with-children-bronx-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6a792ff56ec40f7bd933388c3e6a413-group-leader-partnership-with-children-kings-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/605e5a36e0304c11ba20c866fdfaec48-group-leader-partnership-with-children-kings-county</t>
+  </si>
+  <si>
     <t>House Manager</t>
   </si>
   <si>
@@ -871,6 +1771,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/830914a5300d4d75a281d3c955f6040a-house-manager-imago-dei-ministries-el-cajon</t>
   </si>
   <si>
+    <t>Housing Justice Project King County Legal Assistant (Part time)</t>
+  </si>
+  <si>
+    <t>King County Bar Association, Seattle, WA</t>
+  </si>
+  <si>
+    <t>Kent, Washington</t>
+  </si>
+  <si>
+    <t>USD 31.53 - 32.99/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7656a72bf114538bf01f67772fb5ee4-housing-justice-project-king-county-legal-assistant-part-time-king-county-bar-association-seattle-wa-kent</t>
+  </si>
+  <si>
+    <t>Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8e17fad54e24dabb26af6f37975c045-immigration-staff-attorney-african-communities-together-new-york</t>
+  </si>
+  <si>
     <t>In-Home Counselor/Social Worker (serving Baxter, Boone, and Marion counties)</t>
   </si>
   <si>
@@ -895,6 +1822,180 @@
     <t>https://www.idealist.org/en/nonprofit-job/807feabf71dc459998af1aaa9f28bd59-in-home-counselorsocial-worker-serving-baxter-boone-and-marion-counties-youth-villages-yellville</t>
   </si>
   <si>
+    <t>Individual and Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Chicago Humanities Festival</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78ad57b0c57c4229bf1abd378c0866f8-individual-and-major-gifts-officer-chicago-humanities-festival-chicago</t>
+  </si>
+  <si>
+    <t>Inspection Program Coordinator</t>
+  </si>
+  <si>
+    <t>PCO</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e21105100acd4106ba963c36e33cfddd-inspection-program-coordinator-pco-spring-mills</t>
+  </si>
+  <si>
+    <t>Integrated Mental Health Clinician (LICSW/LMHC)</t>
+  </si>
+  <si>
+    <t>Planned Parenthood of Northern New England</t>
+  </si>
+  <si>
+    <t>Hartford, Vermont</t>
+  </si>
+  <si>
+    <t>USD 36.67 - 36.67/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/637f8e1a8b7a4b9bb90c157643184fdf-integrated-mental-health-clinician-licswlmhc-planned-parenthood-of-northern-new-england-hartford</t>
+  </si>
+  <si>
+    <t>Interfaith Chaplain</t>
+  </si>
+  <si>
+    <t>Attleboro Area Interfaith Collaborative</t>
+  </si>
+  <si>
+    <t>Attleboro, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 31.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Housing Homelessness, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/155ee2dba27e451aa5224c985377d62a-interfaith-chaplain-attleboro-area-interfaith-collaborative-attleboro</t>
+  </si>
+  <si>
+    <t>Interim Managing Director of Programs</t>
+  </si>
+  <si>
+    <t>Shanti Project of San Francisco</t>
+  </si>
+  <si>
+    <t>Animals, Disability, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8267aea57add444ba8559779594b745c-interim-managing-director-of-programs-shanti-project-of-san-francisco-san-francisco</t>
+  </si>
+  <si>
+    <t>Law and STAY FLY Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Fresh Lifelines for Youth</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 27.53 - 27.53/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/790cb482254f4345b0ff818efa015c37-law-and-stay-fly-programs-coordinator-fresh-lifelines-for-youth-san-jose</t>
+  </si>
+  <si>
+    <t>Lead Day Program Instructor (On-Site)</t>
+  </si>
+  <si>
+    <t>Inclusive World</t>
+  </si>
+  <si>
+    <t>Milpitas, California</t>
+  </si>
+  <si>
+    <t>USD 23.50/hour</t>
+  </si>
+  <si>
+    <t>Disability, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1af38e05e9a94af98591cd27061d62c9-lead-day-program-instructor-on-site-inclusive-world-milpitas</t>
+  </si>
+  <si>
+    <t>Leahy Resource Center Staff - Full Time, Weekday</t>
+  </si>
+  <si>
+    <t>Upper Valley Haven</t>
+  </si>
+  <si>
+    <t>USD 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8636d18abd144154986a8ad71879a962-leahy-resource-center-staff-full-time-weekday-upper-valley-haven-hartford</t>
+  </si>
+  <si>
+    <t>Leahy Shelter Staff</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a9c91328e844602ab8b8cb16049d9cd-leahy-shelter-staff-upper-valley-haven-hartford</t>
+  </si>
+  <si>
+    <t>Membership Coordinator/Manager</t>
+  </si>
+  <si>
+    <t>Human Rights Campaign</t>
+  </si>
+  <si>
+    <t>USD 55100.00 - 61000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f669fdd588e94e758715fc00dc86c3a0-membership-coordinatormanager-human-rights-campaign-washington</t>
+  </si>
+  <si>
+    <t>Membership Director</t>
+  </si>
+  <si>
+    <t>AcademyHealth</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a4095ee4cd64c0785c63094094026ba-membership-director-academyhealth-washington</t>
+  </si>
+  <si>
+    <t>Nonprofit Staff Attorney</t>
+  </si>
+  <si>
+    <t>Community Action Program Legal Services, Inc</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e605b304ed6b4ad8992f4d2643eeff6e-nonprofit-staff-attorney-community-action-program-legal-services-inc-boston</t>
+  </si>
+  <si>
     <t>NSD Clinician</t>
   </si>
   <si>
@@ -907,6 +2008,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca819680afce40e8bb709950e4430288-nsd-clinician-together-for-youth-canaan</t>
   </si>
   <si>
+    <t>Occupational Therapist (part-time)</t>
+  </si>
+  <si>
+    <t>New School San Francisco</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 100.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/400578e10b05464495fda45758450111-occupational-therapist-part-time-new-school-san-francisco-san-francisco</t>
+  </si>
+  <si>
+    <t>Operations and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Jewish Solar Challenge</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ef15450f6e242ca8fd95aeb20e3c4ff-operations-and-communications-coordinator-jewish-solar-challenge-los-angeles</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -925,6 +2053,117 @@
     <t>https://www.idealist.org/en/nonprofit-job/1c828973baa04a9daa54224399ab5c38-operations-manager-diabetes-camping-educational-services-orange</t>
   </si>
   <si>
+    <t>Organizing Director - Iowa</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Des Moines, iowa</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 82200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e42fae0123204e2d96b709d62b932179-organizing-director-iowa-the-outreach-team-des-moines</t>
+  </si>
+  <si>
+    <t>Organizing Director- Nebraska</t>
+  </si>
+  <si>
+    <t>Omaha, Nebraska</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c319af5b6f5c4aa3afe94ddbbb152277-organizing-director-nebraska-the-outreach-team-omaha</t>
+  </si>
+  <si>
+    <t>Oslo Freedom Forum Norway Producer</t>
+  </si>
+  <si>
+    <t>Human Rights Foundation</t>
+  </si>
+  <si>
+    <t>Oslo, Oslo, NO</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8c2852be34042388b954e26b7c6d1ab-oslo-freedom-forum-norway-producer-human-rights-foundation-oslo</t>
+  </si>
+  <si>
+    <t>Paralegal (Stay Housed LA) – Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 54080.00 - 71165.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1889cf9ab20401193e0c0f0b366bbe2-paralegal-stay-housed-la-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Part-Time Grants Writer / Events</t>
+  </si>
+  <si>
+    <t>Making Headway Foundation</t>
+  </si>
+  <si>
+    <t>Chappaqua, New York</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f970b2fd1d5f444585e9cf1532b81cfe-part-time-grants-writer-events-making-headway-foundation-chappaqua</t>
+  </si>
+  <si>
+    <t>Personal/Executive Assistant to the CEO</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9be131cc28d2479d86787e08c1da29ac-personalexecutive-assistant-to-the-ceo-los-angeles</t>
+  </si>
+  <si>
+    <t>Policy Associate - J-PAL North America</t>
+  </si>
+  <si>
+    <t>Abdul Latif Jameel Poverty Action Lab, MIT</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 69294.00 - 74624.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8b95fb3b0db4f6e8e22bd7c29239697-policy-associate-j-pal-north-america-abdul-latif-jameel-poverty-action-lab-mit-cambridge</t>
+  </si>
+  <si>
+    <t>Program &amp; Governance Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Community Foundation of South Jersey</t>
+  </si>
+  <si>
+    <t>Camden, New Jersey</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aea03b84bddb4df8b59e650c61b26f2a-program-governance-operations-coordinator-community-foundation-of-south-jersey-camden</t>
+  </si>
+  <si>
     <t>Program Design Lead [Education], Varanasi</t>
   </si>
   <si>
@@ -958,6 +2197,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/9155366247e44b72950d9a37b7944b11-programme-head-early-childhood-care-and-education-ecce-ground-zero-mumbai</t>
   </si>
   <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c12cf74b87c34f6b85a2dd8176395fd1-project-coordinator-african-communities-together-new-york</t>
+  </si>
+  <si>
+    <t>Regional Campaign Manager, Southwest</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/515ec003b9f4464798870e3a291e2260-regional-campaign-manager-southwest-greenlight-america-washington</t>
+  </si>
+  <si>
     <t>Regional Manager – Learning, Monitoring &amp; Evaluation (LME), Patna/Ranchi</t>
   </si>
   <si>
@@ -970,6 +2230,156 @@
     <t>https://www.idealist.org/en/nonprofit-job/abd3ec1d8cfd4704a32740b2543bcf8b-regional-manager-learning-monitoring-evaluation-lme-patnaranchi-ground-zero-patnaranchi</t>
   </si>
   <si>
+    <t>Regional Organizer – Hudson Valley</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ea726b4b54140b498b174c6d1fe28aa-regional-organizer-hudson-valley-new-yorkers-united-for-child-care-new-york</t>
+  </si>
+  <si>
+    <t>Regional Organizer – Long Island</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/936d27fef1724d81aa166554e6e9b496-regional-organizer-long-island-new-yorkers-united-for-child-care-new-york</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Colchester, VT</t>
+  </si>
+  <si>
+    <t>USD 63122.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a94c2cd273ea49c6acef1b543ac7a38e-senior-accountant-planned-parenthood-of-northern-new-england-colchester</t>
+  </si>
+  <si>
+    <t>Senior Director of Communications</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57353f7a74943e89a80322b415b9bcc-senior-director-of-communications-baltimores-promise-baltimore</t>
+  </si>
+  <si>
+    <t>Senior Domestic Policy Analyst</t>
+  </si>
+  <si>
+    <t>Bread for the World, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71d4e15cfd194bda8456739b99b03cb6-senior-domestic-policy-analyst-bread-for-the-world-inc-washington</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7722cfdc6a2423da9de5db47e3112d1-senior-forest-ecologist-the-wilderness-society-washington</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79faa3a0487b4e34a27bc44c4e62f47e-senior-staff-attorney-project-citizenship-boston</t>
+  </si>
+  <si>
+    <t>Social Media and Community Outreach Manager</t>
+  </si>
+  <si>
+    <t>CareHaven</t>
+  </si>
+  <si>
+    <t>Remote (Birmingham, Alabama)</t>
+  </si>
+  <si>
+    <t>USD 15.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Mental Health, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/4bd51f5f13614746bc590d8a76c59b1a-social-media-and-community-outreach-manager-carehaven-birmingham</t>
+  </si>
+  <si>
+    <t>Social Worker/ LMHC at School Based Program</t>
+  </si>
+  <si>
+    <t>Upper Manhattan Mental Health Center, Inc.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10df85be63df4cd4aa2da0295b2598b8-social-worker-lmhc-at-school-based-program-upper-manhattan-mental-health-center-inc-new-york</t>
+  </si>
+  <si>
+    <t>Solar Project Coordinator</t>
+  </si>
+  <si>
+    <t>Municipal Solar Partners</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5291b58cd3324be8b4c12d8b20c5b254-solar-project-coordinator-municipal-solar-partners-providence</t>
+  </si>
+  <si>
+    <t>South Dakota Families for Vaccines Director</t>
+  </si>
+  <si>
+    <t>American Families for Vaccines</t>
+  </si>
+  <si>
+    <t>Remote (South Dakota)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c99189334c844b99ba4067804f97e45-south-dakota-families-for-vaccines-director-american-families-for-vaccines-portland</t>
+  </si>
+  <si>
+    <t>Spanish-speaking Litigation Assistant</t>
+  </si>
+  <si>
+    <t>Prison Law Office</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 77159.00 - 77159.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21da41ed9ef84a5ea2bd713237bc8845-spanish-speaking-litigation-assistant-prison-law-office-berkeley</t>
+  </si>
+  <si>
     <t>Specialist, News &amp; Editorial</t>
   </si>
   <si>
@@ -985,6 +2395,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/b55343843053401b94bb25b80c90b5fd-specialist-news-editorial-american-society-of-clinical-oncology-alexandria</t>
   </si>
   <si>
+    <t>Sr. Director of Strategic Communications &amp; Investor Experience</t>
+  </si>
+  <si>
+    <t>Unite America</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7696b5b4f0b94f19800cf9995a914288-sr-director-of-strategic-communications-investor-experience-unite-america-denver</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5ab3ce72792413386052e8e014a8e62-staff-accountant-unite-america-denver</t>
+  </si>
+  <si>
+    <t>Staff Attorney or Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Just Neighbors: Immigration Legal Services</t>
+  </si>
+  <si>
+    <t>Annandale, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65500.00 - 78500.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Victim Support, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb9fc64d5ebd42f790f3dc95340edb67-staff-attorney-or-senior-staff-attorney-just-neighbors-immigration-legal-services-annandale</t>
+  </si>
+  <si>
     <t>State Gender Coordinator (Education) - Bhubaneshwar, Odisha</t>
   </si>
   <si>
@@ -1009,6 +2464,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ec638999aa44258adc04f463c27f574-state-head-education-chattisgarh-raipur-ground-zero-raipur</t>
   </si>
   <si>
+    <t>Success Coaches</t>
+  </si>
+  <si>
+    <t>Hispanic Unity of Florida</t>
+  </si>
+  <si>
+    <t>Hallandale Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65b0520ee9fc4029a90f03558a622720-success-coaches-hispanic-unity-of-florida-hallandale-beach</t>
+  </si>
+  <si>
     <t>Sunday School Teacher</t>
   </si>
   <si>
@@ -1024,6 +2497,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/157cca625d054333b0577a3277ac20ea-sunday-school-teacher-st-marks-church-in-the-bowery-new-york</t>
   </si>
   <si>
+    <t>Supervisión de Innovación de Trabajadoras Comunitarias de Salud (enfoque en Salud Mental)</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 21000.00 - 21000.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccaa56ec467b43f6b47293e7e9045278-supervision-de-innovacion-de-trabajadoras-comunitarias-de-salud-enfoque-en-salud-mental-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Talent Relations Strategist</t>
+  </si>
+  <si>
+    <t>The Humane League</t>
+  </si>
+  <si>
+    <t>USD 113864.00 - 138737.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66571cd3c0954df29b07b1d70224e685-talent-relations-strategist-the-humane-league-philadelphia</t>
+  </si>
+  <si>
     <t>Training Manager, Immigration Legal Services</t>
   </si>
   <si>
@@ -1037,6 +2543,504 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/363f72ec96b04031ba266af06c3f703a-training-manager-immigration-legal-services-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>Edible Schoolyard NYC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8624ac3344bf41cd978d6c773788cba4-vice-president-of-programs-edible-schoolyard-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Women Building Rhode Island Program Director</t>
+  </si>
+  <si>
+    <t>Building Futures (Rhode Island)</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86d9f084a2b6422e969a6ed5422db110-women-building-rhode-island-program-director-building-futures-rhode-island-providence</t>
+  </si>
+  <si>
+    <t>Youth and Families Project Manager</t>
+  </si>
+  <si>
+    <t>Tilth Alliance</t>
+  </si>
+  <si>
+    <t>USD 24.50 - 24.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b1d80f28f6848ebb0ec9e56a97d70d4-youth-and-families-project-manager-tilth-alliance-seattle</t>
+  </si>
+  <si>
+    <t>Youth Development Recruitment Associate</t>
+  </si>
+  <si>
+    <t>Read Alliance</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a16e7eb9ee4846c5a9815954a77c00a1-youth-development-recruitment-associate-read-alliance-new-york</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>LEE COUNTY CLEMSON EXTENSION OFFICE - Clemson University</t>
+  </si>
+  <si>
+    <t>Bishopville, South Carolina</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72568149</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE COORDINATOR</t>
+  </si>
+  <si>
+    <t>Sustainable Farming Association</t>
+  </si>
+  <si>
+    <t>Hybrid in Northeast Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72564483</t>
+  </si>
+  <si>
+    <t>BUILDINGS AND GROUNDS TECHNICIAN</t>
+  </si>
+  <si>
+    <t>Cottage Grove, Minnesota</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72612141</t>
+  </si>
+  <si>
+    <t>CHIEF ADVANCEMENT OFFICER</t>
+  </si>
+  <si>
+    <t>Coastal Roots Farm</t>
+  </si>
+  <si>
+    <t>Encinitas, California</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72608475</t>
+  </si>
+  <si>
+    <t>CHILD NUTRITION PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Project Bread</t>
+  </si>
+  <si>
+    <t>East Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72574259</t>
+  </si>
+  <si>
+    <t>COMMUNICATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Maine Association of Nonprofits</t>
+  </si>
+  <si>
+    <t>Brunswick, Maine</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72566927</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Fresh Truck</t>
+  </si>
+  <si>
+    <t>Roxbury, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72576703</t>
+  </si>
+  <si>
+    <t>COMMUNITY OUTREACH WORKER</t>
+  </si>
+  <si>
+    <t>EFNEP - BILINGUAL - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72592589</t>
+  </si>
+  <si>
+    <t>CONTROLS TECHNICIAN</t>
+  </si>
+  <si>
+    <t>Straus Family Creamery</t>
+  </si>
+  <si>
+    <t>Rohnert Park, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72606031</t>
+  </si>
+  <si>
+    <t>COPY EDITOR</t>
+  </si>
+  <si>
+    <t>COLLEGE OF ACES - EXTENSION MARKETING AND COMMUNICATIONS - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Urbana, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72598699</t>
+  </si>
+  <si>
+    <t>CURBSIDE MARKET OPERATOR</t>
+  </si>
+  <si>
+    <t>Foodlink</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72575481</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72609697</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Field and Fork Networkâ€¯</t>
+  </si>
+  <si>
+    <t>Hybrid in Buffalo, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72584035</t>
+  </si>
+  <si>
+    <t>DIRECTOR</t>
+  </si>
+  <si>
+    <t>SUPPLY CHAIN - Straus Family Creamery</t>
+  </si>
+  <si>
+    <t>Petaluma, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72604809</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF PROGRAMS</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72610919</t>
+  </si>
+  <si>
+    <t>EXECUTIVE ASSISTANT AND OFFICE MANAGER</t>
+  </si>
+  <si>
+    <t>FRESHFARM</t>
+  </si>
+  <si>
+    <t>Hybrid in Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72580369</t>
+  </si>
+  <si>
+    <t>EXTENSION EDUCATOR</t>
+  </si>
+  <si>
+    <t>4-H YOUTH DEVELOPMENT - STEAM AG - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Bourbonnais, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72591367</t>
+  </si>
+  <si>
+    <t>AGRICULTURE AND AGRIBUSINESS - LOCAL FOOD SYSTEMS AND SMALL FARMS - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Murphysboro, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72597477</t>
+  </si>
+  <si>
+    <t>EXTENSION EDUCATOR AND HEALTH AND COMMUNITY WELLNESS</t>
+  </si>
+  <si>
+    <t>FOOD AND HEALTH SYSTEMS - MURPHYSBORO - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72586479</t>
+  </si>
+  <si>
+    <t>FOOD AND HEALTH SYSTEMS- CHAMPAIGN - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Champaign, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72587701</t>
+  </si>
+  <si>
+    <t>EXTENSION PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>COMMUNITY HEALTH - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Mattteson, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72588923</t>
+  </si>
+  <si>
+    <t>4-H - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Vienna, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72595033</t>
+  </si>
+  <si>
+    <t>ANR - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Woodstock, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72596255</t>
+  </si>
+  <si>
+    <t>FARM MANAGEMENT OUTREACH SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72573037</t>
+  </si>
+  <si>
+    <t>FOOD RECOVERY DRIVER</t>
+  </si>
+  <si>
+    <t>Neighborhood Food Pantries</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72601143</t>
+  </si>
+  <si>
+    <t>FOOD SYSTEMS MARKETING MANAGER</t>
+  </si>
+  <si>
+    <t>Local First Arizona</t>
+  </si>
+  <si>
+    <t>Hybrid in Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72579147</t>
+  </si>
+  <si>
+    <t>GARDEN EDUCATOR</t>
+  </si>
+  <si>
+    <t>Gardobia Gardens</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72565705</t>
+  </si>
+  <si>
+    <t>GRANTS FINANCE MANAGER</t>
+  </si>
+  <si>
+    <t>Accelerating Appalachia</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72562039</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72563261</t>
+  </si>
+  <si>
+    <t>LEAD</t>
+  </si>
+  <si>
+    <t>SUPPLEMENTAL NUTRITION ASSISTANCE PROGRAM - SNAP - National Council on Aging</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72603587</t>
+  </si>
+  <si>
+    <t>MARKET DIRECTOR</t>
+  </si>
+  <si>
+    <t>Dane County Farmers Market</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72577925</t>
+  </si>
+  <si>
+    <t>MARKETING COORDINATOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72607253</t>
+  </si>
+  <si>
+    <t>OFFICE SUPPORT ASSISTANT</t>
+  </si>
+  <si>
+    <t>University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Salem, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72593811</t>
+  </si>
+  <si>
+    <t>OPERATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>Southeastern African American Farmers Organic Network</t>
+  </si>
+  <si>
+    <t>Remote in Georgia, Georgia</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72582813</t>
+  </si>
+  <si>
+    <t>PROGRAM OFFICER</t>
+  </si>
+  <si>
+    <t>Albertsons Companies Foundation</t>
+  </si>
+  <si>
+    <t>Pleasanton, California</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72581591</t>
+  </si>
+  <si>
+    <t>PROGRAMS AND OPERATIONS ASSISTANT</t>
+  </si>
+  <si>
+    <t>Appalachian Resource Conservation and Development Council</t>
+  </si>
+  <si>
+    <t>Johnson City, Tennessee</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72570593</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72571815</t>
+  </si>
+  <si>
+    <t>SENIOR MANAGER</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT AND COMMUNICATIONS - AfriThrive Inc</t>
+  </si>
+  <si>
+    <t>Hybrid in Maryland, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72585257</t>
+  </si>
+  <si>
+    <t>SENIOR VICE PRESIDENT</t>
+  </si>
+  <si>
+    <t>OPERATIONS - Maryland Food Bank</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72599921</t>
+  </si>
+  <si>
+    <t>SHEPARD FARM MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72613363</t>
+  </si>
+  <si>
+    <t>SOLIDARITY ECONOMIES IN AGROECOLOGY PROJECT MANAGER</t>
+  </si>
+  <si>
+    <t>Community Agroecology Network</t>
+  </si>
+  <si>
+    <t>Hybrid in Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72569371</t>
+  </si>
+  <si>
+    <t>SUPPLY CHAIN MANAGER</t>
+  </si>
+  <si>
+    <t>World Central Kitchen</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72602365</t>
   </si>
 </sst>
 </file>
@@ -1575,606 +3579,609 @@
       <c r="F6" t="s">
         <v>37</v>
       </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
         <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2219,7 +4226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2258,8 +4265,88 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2267,7 +4354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2308,741 +4395,3277 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D4" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="E11" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="F13" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="E14" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F14" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E15" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
-        <v>252</v>
+        <v>268</v>
+      </c>
+      <c r="G15" t="s">
+        <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="F16" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E17" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="F17" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="F18" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C19" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="E19" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="F19" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E21" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="F21" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B22" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E22" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="F22" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>302</v>
       </c>
       <c r="C23" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F25" t="s">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B26" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C26" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="F26" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>324</v>
       </c>
       <c r="C27" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E27" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="F27" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
       <c r="C28" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E28" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="F28" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B29" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="C29" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E29" t="s">
-        <v>200</v>
+        <v>338</v>
       </c>
       <c r="F29" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>342</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>186</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E30" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="F30" t="s">
-        <v>212</v>
+        <v>344</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>347</v>
       </c>
       <c r="C31" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E31" t="s">
-        <v>329</v>
+        <v>218</v>
       </c>
       <c r="F31" t="s">
-        <v>212</v>
+        <v>349</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C32" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E32" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="F32" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>359</v>
       </c>
       <c r="D33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" t="s">
+        <v>360</v>
+      </c>
+      <c r="F33" t="s">
+        <v>361</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>363</v>
+      </c>
+      <c r="B34" t="s">
+        <v>302</v>
+      </c>
+      <c r="C34" t="s">
+        <v>364</v>
+      </c>
+      <c r="D34" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F34" t="s">
+        <v>305</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>363</v>
+      </c>
+      <c r="B35" t="s">
+        <v>302</v>
+      </c>
+      <c r="C35" t="s">
+        <v>303</v>
+      </c>
+      <c r="D35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" t="s">
+        <v>304</v>
+      </c>
+      <c r="F35" t="s">
+        <v>305</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>367</v>
+      </c>
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" t="s">
         <v>186</v>
       </c>
-      <c r="E33" t="s">
-        <v>338</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D36" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" t="s">
+        <v>369</v>
+      </c>
+      <c r="F36" t="s">
+        <v>242</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>371</v>
+      </c>
+      <c r="B37" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" t="s">
+        <v>201</v>
+      </c>
+      <c r="E37" t="s">
+        <v>374</v>
+      </c>
+      <c r="F37" t="s">
+        <v>375</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>377</v>
+      </c>
+      <c r="B38" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" t="s">
+        <v>263</v>
+      </c>
+      <c r="E38" t="s">
+        <v>378</v>
+      </c>
+      <c r="F38" t="s">
+        <v>379</v>
+      </c>
+      <c r="G38" t="s">
+        <v>380</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>382</v>
+      </c>
+      <c r="B39" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" t="s">
+        <v>201</v>
+      </c>
+      <c r="E39" t="s">
+        <v>384</v>
+      </c>
+      <c r="F39" t="s">
+        <v>385</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>387</v>
+      </c>
+      <c r="B40" t="s">
+        <v>388</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" t="s">
+        <v>389</v>
+      </c>
+      <c r="F40" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>391</v>
+      </c>
+      <c r="B41" t="s">
+        <v>392</v>
+      </c>
+      <c r="C41" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" t="s">
+        <v>384</v>
+      </c>
+      <c r="F41" t="s">
+        <v>393</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>395</v>
+      </c>
+      <c r="B42" t="s">
+        <v>392</v>
+      </c>
+      <c r="C42" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" t="s">
+        <v>396</v>
+      </c>
+      <c r="F42" t="s">
+        <v>393</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>398</v>
+      </c>
+      <c r="B43" t="s">
+        <v>399</v>
+      </c>
+      <c r="C43" t="s">
+        <v>400</v>
+      </c>
+      <c r="D43" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" t="s">
+        <v>401</v>
+      </c>
+      <c r="F43" t="s">
+        <v>402</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>404</v>
+      </c>
+      <c r="B44" t="s">
+        <v>405</v>
+      </c>
+      <c r="C44" t="s">
+        <v>406</v>
+      </c>
+      <c r="D44" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" t="s">
+        <v>407</v>
+      </c>
+      <c r="F44" t="s">
+        <v>408</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>404</v>
+      </c>
+      <c r="B45" t="s">
+        <v>410</v>
+      </c>
+      <c r="C45" t="s">
+        <v>411</v>
+      </c>
+      <c r="D45" t="s">
+        <v>201</v>
+      </c>
+      <c r="E45" t="s">
+        <v>412</v>
+      </c>
+      <c r="F45" t="s">
+        <v>413</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>415</v>
+      </c>
+      <c r="B46" t="s">
+        <v>416</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" t="s">
+        <v>417</v>
+      </c>
+      <c r="F46" t="s">
+        <v>418</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" t="s">
+        <v>421</v>
+      </c>
+      <c r="C47" t="s">
+        <v>222</v>
+      </c>
+      <c r="D47" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" t="s">
+        <v>422</v>
+      </c>
+      <c r="F47" t="s">
+        <v>423</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>425</v>
+      </c>
+      <c r="B48" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" t="s">
+        <v>228</v>
+      </c>
+      <c r="D48" t="s">
+        <v>201</v>
+      </c>
+      <c r="E48" t="s">
+        <v>427</v>
+      </c>
+      <c r="F48" t="s">
+        <v>428</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>430</v>
+      </c>
+      <c r="B49" t="s">
+        <v>431</v>
+      </c>
+      <c r="C49" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" t="s">
+        <v>201</v>
+      </c>
+      <c r="E49" t="s">
+        <v>432</v>
+      </c>
+      <c r="F49" t="s">
+        <v>433</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>435</v>
+      </c>
+      <c r="B50" t="s">
+        <v>436</v>
+      </c>
+      <c r="C50" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" t="s">
+        <v>437</v>
+      </c>
+      <c r="F50" t="s">
+        <v>438</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>440</v>
+      </c>
+      <c r="B51" t="s">
+        <v>441</v>
+      </c>
+      <c r="C51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51" t="s">
+        <v>442</v>
+      </c>
+      <c r="F51" t="s">
+        <v>443</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>445</v>
+      </c>
+      <c r="B52" t="s">
+        <v>446</v>
+      </c>
+      <c r="C52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E52" t="s">
+        <v>447</v>
+      </c>
+      <c r="F52" t="s">
+        <v>448</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>450</v>
+      </c>
+      <c r="B53" t="s">
+        <v>451</v>
+      </c>
+      <c r="C53" t="s">
+        <v>452</v>
+      </c>
+      <c r="D53" t="s">
+        <v>201</v>
+      </c>
+      <c r="E53" t="s">
+        <v>290</v>
+      </c>
+      <c r="F53" t="s">
+        <v>253</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>454</v>
+      </c>
+      <c r="B54" t="s">
+        <v>455</v>
+      </c>
+      <c r="C54" t="s">
+        <v>456</v>
+      </c>
+      <c r="D54" t="s">
+        <v>201</v>
+      </c>
+      <c r="E54" t="s">
+        <v>457</v>
+      </c>
+      <c r="F54" t="s">
+        <v>458</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>460</v>
+      </c>
+      <c r="B55" t="s">
+        <v>461</v>
+      </c>
+      <c r="C55" t="s">
+        <v>462</v>
+      </c>
+      <c r="D55" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" t="s">
+        <v>463</v>
+      </c>
+      <c r="F55" t="s">
+        <v>464</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>466</v>
+      </c>
+      <c r="B56" t="s">
+        <v>467</v>
+      </c>
+      <c r="C56" t="s">
+        <v>468</v>
+      </c>
+      <c r="D56" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" t="s">
+        <v>253</v>
+      </c>
+      <c r="F56" t="s">
+        <v>253</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>470</v>
+      </c>
+      <c r="B57" t="s">
+        <v>471</v>
+      </c>
+      <c r="C57" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E57" t="s">
+        <v>472</v>
+      </c>
+      <c r="F57" t="s">
+        <v>473</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>475</v>
+      </c>
+      <c r="B58" t="s">
+        <v>476</v>
+      </c>
+      <c r="C58" t="s">
+        <v>284</v>
+      </c>
+      <c r="D58" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" t="s">
+        <v>477</v>
+      </c>
+      <c r="F58" t="s">
+        <v>478</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>480</v>
+      </c>
+      <c r="B59" t="s">
+        <v>481</v>
+      </c>
+      <c r="C59" t="s">
+        <v>186</v>
+      </c>
+      <c r="D59" t="s">
+        <v>201</v>
+      </c>
+      <c r="E59" t="s">
+        <v>482</v>
+      </c>
+      <c r="F59" t="s">
+        <v>483</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>485</v>
+      </c>
+      <c r="B60" t="s">
+        <v>486</v>
+      </c>
+      <c r="C60" t="s">
+        <v>487</v>
+      </c>
+      <c r="D60" t="s">
+        <v>201</v>
+      </c>
+      <c r="E60" t="s">
+        <v>488</v>
+      </c>
+      <c r="F60" t="s">
+        <v>489</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>491</v>
+      </c>
+      <c r="B61" t="s">
+        <v>492</v>
+      </c>
+      <c r="C61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" t="s">
+        <v>493</v>
+      </c>
+      <c r="F61" t="s">
         <v>339</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>340</v>
+      <c r="H61" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>495</v>
+      </c>
+      <c r="B62" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" t="s">
+        <v>320</v>
+      </c>
+      <c r="D62" t="s">
+        <v>208</v>
+      </c>
+      <c r="E62" t="s">
+        <v>496</v>
+      </c>
+      <c r="F62" t="s">
+        <v>253</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>498</v>
+      </c>
+      <c r="B63" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63" t="s">
+        <v>320</v>
+      </c>
+      <c r="D63" t="s">
+        <v>201</v>
+      </c>
+      <c r="E63" t="s">
+        <v>499</v>
+      </c>
+      <c r="F63" t="s">
+        <v>253</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>501</v>
+      </c>
+      <c r="B64" t="s">
+        <v>502</v>
+      </c>
+      <c r="C64" t="s">
+        <v>503</v>
+      </c>
+      <c r="D64" t="s">
+        <v>201</v>
+      </c>
+      <c r="E64" t="s">
+        <v>504</v>
+      </c>
+      <c r="F64" t="s">
+        <v>505</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>507</v>
+      </c>
+      <c r="B65" t="s">
+        <v>508</v>
+      </c>
+      <c r="C65" t="s">
+        <v>509</v>
+      </c>
+      <c r="D65" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" t="s">
+        <v>396</v>
+      </c>
+      <c r="F65" t="s">
+        <v>510</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" t="s">
+        <v>512</v>
+      </c>
+      <c r="C66" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" t="s">
+        <v>513</v>
+      </c>
+      <c r="F66" t="s">
+        <v>514</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>516</v>
+      </c>
+      <c r="C67" t="s">
+        <v>517</v>
+      </c>
+      <c r="D67" t="s">
+        <v>201</v>
+      </c>
+      <c r="E67" t="s">
+        <v>518</v>
+      </c>
+      <c r="F67" t="s">
+        <v>253</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>520</v>
+      </c>
+      <c r="B68" t="s">
+        <v>521</v>
+      </c>
+      <c r="C68" t="s">
+        <v>522</v>
+      </c>
+      <c r="D68" t="s">
+        <v>201</v>
+      </c>
+      <c r="E68" t="s">
+        <v>523</v>
+      </c>
+      <c r="F68" t="s">
+        <v>524</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>520</v>
+      </c>
+      <c r="B69" t="s">
+        <v>526</v>
+      </c>
+      <c r="C69" t="s">
+        <v>487</v>
+      </c>
+      <c r="D69" t="s">
+        <v>201</v>
+      </c>
+      <c r="E69" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" t="s">
+        <v>527</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>520</v>
+      </c>
+      <c r="B70" t="s">
+        <v>529</v>
+      </c>
+      <c r="C70" t="s">
+        <v>222</v>
+      </c>
+      <c r="D70" t="s">
+        <v>201</v>
+      </c>
+      <c r="E70" t="s">
+        <v>530</v>
+      </c>
+      <c r="F70" t="s">
+        <v>531</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>533</v>
+      </c>
+      <c r="B71" t="s">
+        <v>534</v>
+      </c>
+      <c r="C71" t="s">
+        <v>535</v>
+      </c>
+      <c r="D71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E71" t="s">
+        <v>290</v>
+      </c>
+      <c r="F71" t="s">
+        <v>536</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>538</v>
+      </c>
+      <c r="B72" t="s">
+        <v>539</v>
+      </c>
+      <c r="C72" t="s">
+        <v>540</v>
+      </c>
+      <c r="D72" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72" t="s">
+        <v>541</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>543</v>
+      </c>
+      <c r="B73" t="s">
+        <v>544</v>
+      </c>
+      <c r="C73" t="s">
+        <v>545</v>
+      </c>
+      <c r="D73" t="s">
+        <v>208</v>
+      </c>
+      <c r="E73" t="s">
+        <v>546</v>
+      </c>
+      <c r="F73" t="s">
+        <v>547</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>549</v>
+      </c>
+      <c r="B74" t="s">
+        <v>550</v>
+      </c>
+      <c r="C74" t="s">
+        <v>551</v>
+      </c>
+      <c r="D74" t="s">
+        <v>234</v>
+      </c>
+      <c r="E74" t="s">
+        <v>552</v>
+      </c>
+      <c r="F74" t="s">
+        <v>553</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>555</v>
+      </c>
+      <c r="B75" t="s">
+        <v>556</v>
+      </c>
+      <c r="C75" t="s">
+        <v>373</v>
+      </c>
+      <c r="D75" t="s">
+        <v>201</v>
+      </c>
+      <c r="E75" t="s">
+        <v>557</v>
+      </c>
+      <c r="F75" t="s">
+        <v>379</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>559</v>
+      </c>
+      <c r="B76" t="s">
+        <v>560</v>
+      </c>
+      <c r="C76" t="s">
+        <v>284</v>
+      </c>
+      <c r="D76" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" t="s">
+        <v>417</v>
+      </c>
+      <c r="F76" t="s">
+        <v>561</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>563</v>
+      </c>
+      <c r="B77" t="s">
+        <v>564</v>
+      </c>
+      <c r="C77" t="s">
+        <v>222</v>
+      </c>
+      <c r="D77" t="s">
+        <v>201</v>
+      </c>
+      <c r="E77" t="s">
+        <v>565</v>
+      </c>
+      <c r="F77" t="s">
+        <v>566</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>568</v>
+      </c>
+      <c r="B78" t="s">
+        <v>569</v>
+      </c>
+      <c r="C78" t="s">
+        <v>570</v>
+      </c>
+      <c r="D78" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" t="s">
+        <v>571</v>
+      </c>
+      <c r="F78" t="s">
+        <v>572</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>574</v>
+      </c>
+      <c r="B79" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" t="s">
+        <v>575</v>
+      </c>
+      <c r="F79" t="s">
+        <v>210</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>574</v>
+      </c>
+      <c r="B80" t="s">
+        <v>206</v>
+      </c>
+      <c r="C80" t="s">
+        <v>207</v>
+      </c>
+      <c r="D80" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" t="s">
+        <v>575</v>
+      </c>
+      <c r="F80" t="s">
+        <v>210</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>574</v>
+      </c>
+      <c r="B81" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" t="s">
+        <v>207</v>
+      </c>
+      <c r="D81" t="s">
+        <v>208</v>
+      </c>
+      <c r="E81" t="s">
+        <v>575</v>
+      </c>
+      <c r="F81" t="s">
+        <v>210</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>579</v>
+      </c>
+      <c r="B82" t="s">
+        <v>580</v>
+      </c>
+      <c r="C82" t="s">
+        <v>581</v>
+      </c>
+      <c r="D82" t="s">
+        <v>201</v>
+      </c>
+      <c r="E82" t="s">
+        <v>582</v>
+      </c>
+      <c r="F82" t="s">
+        <v>583</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>585</v>
+      </c>
+      <c r="B83" t="s">
+        <v>586</v>
+      </c>
+      <c r="C83" t="s">
+        <v>587</v>
+      </c>
+      <c r="D83" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" t="s">
+        <v>588</v>
+      </c>
+      <c r="F83" t="s">
+        <v>589</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>591</v>
+      </c>
+      <c r="B84" t="s">
+        <v>392</v>
+      </c>
+      <c r="C84" t="s">
+        <v>222</v>
+      </c>
+      <c r="D84" t="s">
+        <v>201</v>
+      </c>
+      <c r="E84" t="s">
+        <v>592</v>
+      </c>
+      <c r="F84" t="s">
+        <v>393</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>594</v>
+      </c>
+      <c r="B85" t="s">
+        <v>595</v>
+      </c>
+      <c r="C85" t="s">
+        <v>596</v>
+      </c>
+      <c r="D85" t="s">
+        <v>201</v>
+      </c>
+      <c r="E85" t="s">
+        <v>597</v>
+      </c>
+      <c r="F85" t="s">
+        <v>598</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>594</v>
+      </c>
+      <c r="B86" t="s">
+        <v>595</v>
+      </c>
+      <c r="C86" t="s">
+        <v>600</v>
+      </c>
+      <c r="D86" t="s">
+        <v>201</v>
+      </c>
+      <c r="E86" t="s">
+        <v>597</v>
+      </c>
+      <c r="F86" t="s">
+        <v>598</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>602</v>
+      </c>
+      <c r="B87" t="s">
+        <v>603</v>
+      </c>
+      <c r="C87" t="s">
+        <v>604</v>
+      </c>
+      <c r="D87" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" t="s">
+        <v>605</v>
+      </c>
+      <c r="F87" t="s">
+        <v>606</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>608</v>
+      </c>
+      <c r="B88" t="s">
+        <v>609</v>
+      </c>
+      <c r="C88" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" t="s">
+        <v>201</v>
+      </c>
+      <c r="E88" t="s">
+        <v>610</v>
+      </c>
+      <c r="F88" t="s">
+        <v>611</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>613</v>
+      </c>
+      <c r="B89" t="s">
+        <v>614</v>
+      </c>
+      <c r="C89" t="s">
+        <v>615</v>
+      </c>
+      <c r="D89" t="s">
+        <v>201</v>
+      </c>
+      <c r="E89" t="s">
+        <v>616</v>
+      </c>
+      <c r="F89" t="s">
+        <v>236</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>618</v>
+      </c>
+      <c r="B90" t="s">
+        <v>619</v>
+      </c>
+      <c r="C90" t="s">
+        <v>620</v>
+      </c>
+      <c r="D90" t="s">
+        <v>208</v>
+      </c>
+      <c r="E90" t="s">
+        <v>621</v>
+      </c>
+      <c r="F90" t="s">
+        <v>622</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>624</v>
+      </c>
+      <c r="B91" t="s">
+        <v>625</v>
+      </c>
+      <c r="C91" t="s">
+        <v>320</v>
+      </c>
+      <c r="D91" t="s">
+        <v>263</v>
+      </c>
+      <c r="E91" t="s">
+        <v>523</v>
+      </c>
+      <c r="F91" t="s">
+        <v>626</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>628</v>
+      </c>
+      <c r="B92" t="s">
+        <v>629</v>
+      </c>
+      <c r="C92" t="s">
+        <v>630</v>
+      </c>
+      <c r="D92" t="s">
+        <v>201</v>
+      </c>
+      <c r="E92" t="s">
+        <v>631</v>
+      </c>
+      <c r="F92" t="s">
+        <v>632</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>634</v>
+      </c>
+      <c r="B93" t="s">
+        <v>635</v>
+      </c>
+      <c r="C93" t="s">
+        <v>636</v>
+      </c>
+      <c r="D93" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" t="s">
+        <v>637</v>
+      </c>
+      <c r="F93" t="s">
+        <v>638</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>640</v>
+      </c>
+      <c r="B94" t="s">
+        <v>641</v>
+      </c>
+      <c r="C94" t="s">
+        <v>615</v>
+      </c>
+      <c r="D94" t="s">
+        <v>201</v>
+      </c>
+      <c r="E94" t="s">
+        <v>642</v>
+      </c>
+      <c r="F94" t="s">
+        <v>402</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>644</v>
+      </c>
+      <c r="B95" t="s">
+        <v>641</v>
+      </c>
+      <c r="C95" t="s">
+        <v>615</v>
+      </c>
+      <c r="D95" t="s">
+        <v>201</v>
+      </c>
+      <c r="E95" t="s">
+        <v>642</v>
+      </c>
+      <c r="F95" t="s">
+        <v>402</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>646</v>
+      </c>
+      <c r="B96" t="s">
+        <v>647</v>
+      </c>
+      <c r="C96" t="s">
+        <v>314</v>
+      </c>
+      <c r="D96" t="s">
+        <v>201</v>
+      </c>
+      <c r="E96" t="s">
+        <v>648</v>
+      </c>
+      <c r="F96" t="s">
+        <v>649</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>651</v>
+      </c>
+      <c r="B97" t="s">
+        <v>652</v>
+      </c>
+      <c r="C97" t="s">
+        <v>186</v>
+      </c>
+      <c r="D97" t="s">
+        <v>201</v>
+      </c>
+      <c r="E97" t="s">
+        <v>653</v>
+      </c>
+      <c r="F97" t="s">
+        <v>654</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>656</v>
+      </c>
+      <c r="B98" t="s">
+        <v>657</v>
+      </c>
+      <c r="C98" t="s">
+        <v>359</v>
+      </c>
+      <c r="D98" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" t="s">
+        <v>253</v>
+      </c>
+      <c r="F98" t="s">
+        <v>658</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>660</v>
+      </c>
+      <c r="B99" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" t="s">
+        <v>331</v>
+      </c>
+      <c r="D99" t="s">
+        <v>201</v>
+      </c>
+      <c r="E99" t="s">
+        <v>661</v>
+      </c>
+      <c r="F99" t="s">
+        <v>662</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>664</v>
+      </c>
+      <c r="B100" t="s">
+        <v>665</v>
+      </c>
+      <c r="C100" t="s">
+        <v>320</v>
+      </c>
+      <c r="D100" t="s">
+        <v>208</v>
+      </c>
+      <c r="E100" t="s">
+        <v>666</v>
+      </c>
+      <c r="F100" t="s">
+        <v>210</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>668</v>
+      </c>
+      <c r="B101" t="s">
+        <v>669</v>
+      </c>
+      <c r="C101" t="s">
+        <v>186</v>
+      </c>
+      <c r="D101" t="s">
+        <v>208</v>
+      </c>
+      <c r="E101" t="s">
+        <v>670</v>
+      </c>
+      <c r="F101" t="s">
+        <v>671</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>673</v>
+      </c>
+      <c r="B102" t="s">
+        <v>674</v>
+      </c>
+      <c r="C102" t="s">
+        <v>675</v>
+      </c>
+      <c r="D102" t="s">
+        <v>201</v>
+      </c>
+      <c r="E102" t="s">
+        <v>676</v>
+      </c>
+      <c r="F102" t="s">
+        <v>677</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>679</v>
+      </c>
+      <c r="B103" t="s">
+        <v>680</v>
+      </c>
+      <c r="C103" t="s">
+        <v>681</v>
+      </c>
+      <c r="D103" t="s">
+        <v>201</v>
+      </c>
+      <c r="E103" t="s">
+        <v>682</v>
+      </c>
+      <c r="F103" t="s">
+        <v>253</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>684</v>
+      </c>
+      <c r="B104" t="s">
+        <v>680</v>
+      </c>
+      <c r="C104" t="s">
+        <v>685</v>
+      </c>
+      <c r="D104" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" t="s">
+        <v>682</v>
+      </c>
+      <c r="F104" t="s">
+        <v>253</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>687</v>
+      </c>
+      <c r="B105" t="s">
+        <v>688</v>
+      </c>
+      <c r="C105" t="s">
+        <v>689</v>
+      </c>
+      <c r="D105" t="s">
+        <v>234</v>
+      </c>
+      <c r="E105" t="s">
+        <v>253</v>
+      </c>
+      <c r="F105" t="s">
+        <v>690</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>692</v>
+      </c>
+      <c r="B106" t="s">
+        <v>693</v>
+      </c>
+      <c r="C106" t="s">
+        <v>456</v>
+      </c>
+      <c r="D106" t="s">
+        <v>201</v>
+      </c>
+      <c r="E106" t="s">
+        <v>694</v>
+      </c>
+      <c r="F106" t="s">
+        <v>658</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>696</v>
+      </c>
+      <c r="B107" t="s">
+        <v>697</v>
+      </c>
+      <c r="C107" t="s">
+        <v>698</v>
+      </c>
+      <c r="D107" t="s">
+        <v>208</v>
+      </c>
+      <c r="E107" t="s">
+        <v>699</v>
+      </c>
+      <c r="F107" t="s">
+        <v>700</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>702</v>
+      </c>
+      <c r="B108" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" t="s">
+        <v>456</v>
+      </c>
+      <c r="D108" t="s">
+        <v>201</v>
+      </c>
+      <c r="E108" t="s">
+        <v>703</v>
+      </c>
+      <c r="F108" t="s">
+        <v>690</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>705</v>
+      </c>
+      <c r="B109" t="s">
+        <v>706</v>
+      </c>
+      <c r="C109" t="s">
+        <v>707</v>
+      </c>
+      <c r="D109" t="s">
+        <v>201</v>
+      </c>
+      <c r="E109" t="s">
+        <v>708</v>
+      </c>
+      <c r="F109" t="s">
+        <v>709</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>711</v>
+      </c>
+      <c r="B110" t="s">
+        <v>712</v>
+      </c>
+      <c r="C110" t="s">
+        <v>713</v>
+      </c>
+      <c r="D110" t="s">
+        <v>246</v>
+      </c>
+      <c r="E110" t="s">
+        <v>670</v>
+      </c>
+      <c r="F110" t="s">
+        <v>714</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>716</v>
+      </c>
+      <c r="B111" t="s">
+        <v>272</v>
+      </c>
+      <c r="C111" t="s">
+        <v>717</v>
+      </c>
+      <c r="D111" t="s">
+        <v>201</v>
+      </c>
+      <c r="E111" t="s">
+        <v>718</v>
+      </c>
+      <c r="F111" t="s">
+        <v>230</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>720</v>
+      </c>
+      <c r="B112" t="s">
+        <v>721</v>
+      </c>
+      <c r="C112" t="s">
+        <v>722</v>
+      </c>
+      <c r="D112" t="s">
+        <v>201</v>
+      </c>
+      <c r="E112" t="s">
+        <v>253</v>
+      </c>
+      <c r="F112" t="s">
+        <v>253</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>724</v>
+      </c>
+      <c r="B113" t="s">
+        <v>272</v>
+      </c>
+      <c r="C113" t="s">
+        <v>273</v>
+      </c>
+      <c r="D113" t="s">
+        <v>201</v>
+      </c>
+      <c r="E113" t="s">
+        <v>725</v>
+      </c>
+      <c r="F113" t="s">
+        <v>230</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114" t="s">
+        <v>392</v>
+      </c>
+      <c r="C114" t="s">
+        <v>222</v>
+      </c>
+      <c r="D114" t="s">
+        <v>246</v>
+      </c>
+      <c r="E114" t="s">
+        <v>727</v>
+      </c>
+      <c r="F114" t="s">
+        <v>393</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>729</v>
+      </c>
+      <c r="B115" t="s">
+        <v>730</v>
+      </c>
+      <c r="C115" t="s">
+        <v>186</v>
+      </c>
+      <c r="D115" t="s">
+        <v>201</v>
+      </c>
+      <c r="E115" t="s">
+        <v>731</v>
+      </c>
+      <c r="F115" t="s">
+        <v>732</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>734</v>
+      </c>
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" t="s">
+        <v>735</v>
+      </c>
+      <c r="D116" t="s">
+        <v>201</v>
+      </c>
+      <c r="E116" t="s">
+        <v>736</v>
+      </c>
+      <c r="F116" t="s">
+        <v>230</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>738</v>
+      </c>
+      <c r="B117" t="s">
+        <v>347</v>
+      </c>
+      <c r="C117" t="s">
+        <v>348</v>
+      </c>
+      <c r="D117" t="s">
+        <v>201</v>
+      </c>
+      <c r="E117" t="s">
+        <v>739</v>
+      </c>
+      <c r="F117" t="s">
+        <v>349</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>741</v>
+      </c>
+      <c r="B118" t="s">
+        <v>347</v>
+      </c>
+      <c r="C118" t="s">
+        <v>348</v>
+      </c>
+      <c r="D118" t="s">
+        <v>201</v>
+      </c>
+      <c r="E118" t="s">
+        <v>739</v>
+      </c>
+      <c r="F118" t="s">
+        <v>349</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>743</v>
+      </c>
+      <c r="B119" t="s">
+        <v>614</v>
+      </c>
+      <c r="C119" t="s">
+        <v>744</v>
+      </c>
+      <c r="D119" t="s">
+        <v>201</v>
+      </c>
+      <c r="E119" t="s">
+        <v>745</v>
+      </c>
+      <c r="F119" t="s">
+        <v>746</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>748</v>
+      </c>
+      <c r="B120" t="s">
+        <v>410</v>
+      </c>
+      <c r="C120" t="s">
+        <v>411</v>
+      </c>
+      <c r="D120" t="s">
+        <v>201</v>
+      </c>
+      <c r="E120" t="s">
+        <v>749</v>
+      </c>
+      <c r="F120" t="s">
+        <v>413</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>751</v>
+      </c>
+      <c r="B121" t="s">
+        <v>752</v>
+      </c>
+      <c r="C121" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" t="s">
+        <v>201</v>
+      </c>
+      <c r="E121" t="s">
+        <v>753</v>
+      </c>
+      <c r="F121" t="s">
+        <v>754</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>191</v>
+      </c>
+      <c r="B122" t="s">
+        <v>185</v>
+      </c>
+      <c r="C122" t="s">
+        <v>186</v>
+      </c>
+      <c r="D122" t="s">
+        <v>201</v>
+      </c>
+      <c r="E122" t="s">
+        <v>756</v>
+      </c>
+      <c r="F122" t="s">
+        <v>757</v>
+      </c>
+      <c r="G122" t="s">
+        <v>380</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>759</v>
+      </c>
+      <c r="B123" t="s">
+        <v>358</v>
+      </c>
+      <c r="C123" t="s">
+        <v>359</v>
+      </c>
+      <c r="D123" t="s">
+        <v>201</v>
+      </c>
+      <c r="E123" t="s">
+        <v>760</v>
+      </c>
+      <c r="F123" t="s">
+        <v>361</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>762</v>
+      </c>
+      <c r="B124" t="s">
+        <v>763</v>
+      </c>
+      <c r="C124" t="s">
+        <v>764</v>
+      </c>
+      <c r="D124" t="s">
+        <v>208</v>
+      </c>
+      <c r="E124" t="s">
+        <v>765</v>
+      </c>
+      <c r="F124" t="s">
+        <v>766</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>768</v>
+      </c>
+      <c r="B125" t="s">
+        <v>769</v>
+      </c>
+      <c r="C125" t="s">
+        <v>222</v>
+      </c>
+      <c r="D125" t="s">
+        <v>201</v>
+      </c>
+      <c r="E125" t="s">
+        <v>770</v>
+      </c>
+      <c r="F125" t="s">
+        <v>771</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>773</v>
+      </c>
+      <c r="B126" t="s">
+        <v>774</v>
+      </c>
+      <c r="C126" t="s">
+        <v>186</v>
+      </c>
+      <c r="D126" t="s">
+        <v>201</v>
+      </c>
+      <c r="E126" t="s">
+        <v>241</v>
+      </c>
+      <c r="F126" t="s">
+        <v>775</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>777</v>
+      </c>
+      <c r="B127" t="s">
+        <v>778</v>
+      </c>
+      <c r="C127" t="s">
+        <v>779</v>
+      </c>
+      <c r="D127" t="s">
+        <v>201</v>
+      </c>
+      <c r="E127" t="s">
+        <v>780</v>
+      </c>
+      <c r="F127" t="s">
+        <v>253</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>782</v>
+      </c>
+      <c r="B128" t="s">
+        <v>783</v>
+      </c>
+      <c r="C128" t="s">
+        <v>784</v>
+      </c>
+      <c r="D128" t="s">
+        <v>201</v>
+      </c>
+      <c r="E128" t="s">
+        <v>785</v>
+      </c>
+      <c r="F128" t="s">
+        <v>786</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>788</v>
+      </c>
+      <c r="B129" t="s">
+        <v>789</v>
+      </c>
+      <c r="C129" t="s">
+        <v>790</v>
+      </c>
+      <c r="D129" t="s">
+        <v>201</v>
+      </c>
+      <c r="E129" t="s">
+        <v>253</v>
+      </c>
+      <c r="F129" t="s">
+        <v>791</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>793</v>
+      </c>
+      <c r="B130" t="s">
+        <v>794</v>
+      </c>
+      <c r="C130" t="s">
+        <v>795</v>
+      </c>
+      <c r="D130" t="s">
+        <v>201</v>
+      </c>
+      <c r="E130" t="s">
+        <v>796</v>
+      </c>
+      <c r="F130" t="s">
+        <v>797</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>799</v>
+      </c>
+      <c r="B131" t="s">
+        <v>794</v>
+      </c>
+      <c r="C131" t="s">
+        <v>795</v>
+      </c>
+      <c r="D131" t="s">
+        <v>201</v>
+      </c>
+      <c r="E131" t="s">
+        <v>800</v>
+      </c>
+      <c r="F131" t="s">
+        <v>448</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>802</v>
+      </c>
+      <c r="B132" t="s">
+        <v>803</v>
+      </c>
+      <c r="C132" t="s">
+        <v>804</v>
+      </c>
+      <c r="D132" t="s">
+        <v>201</v>
+      </c>
+      <c r="E132" t="s">
+        <v>805</v>
+      </c>
+      <c r="F132" t="s">
+        <v>806</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>808</v>
+      </c>
+      <c r="B133" t="s">
+        <v>272</v>
+      </c>
+      <c r="C133" t="s">
+        <v>809</v>
+      </c>
+      <c r="D133" t="s">
+        <v>201</v>
+      </c>
+      <c r="E133" t="s">
+        <v>810</v>
+      </c>
+      <c r="F133" t="s">
+        <v>230</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>812</v>
+      </c>
+      <c r="B134" t="s">
+        <v>272</v>
+      </c>
+      <c r="C134" t="s">
+        <v>813</v>
+      </c>
+      <c r="D134" t="s">
+        <v>201</v>
+      </c>
+      <c r="E134" t="s">
+        <v>814</v>
+      </c>
+      <c r="F134" t="s">
+        <v>230</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>816</v>
+      </c>
+      <c r="B135" t="s">
+        <v>817</v>
+      </c>
+      <c r="C135" t="s">
+        <v>818</v>
+      </c>
+      <c r="D135" t="s">
+        <v>201</v>
+      </c>
+      <c r="E135" t="s">
+        <v>819</v>
+      </c>
+      <c r="F135" t="s">
+        <v>820</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>822</v>
+      </c>
+      <c r="B136" t="s">
+        <v>823</v>
+      </c>
+      <c r="C136" t="s">
+        <v>222</v>
+      </c>
+      <c r="D136" t="s">
+        <v>234</v>
+      </c>
+      <c r="E136" t="s">
+        <v>824</v>
+      </c>
+      <c r="F136" t="s">
+        <v>825</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>827</v>
+      </c>
+      <c r="B137" t="s">
+        <v>828</v>
+      </c>
+      <c r="C137" t="s">
+        <v>829</v>
+      </c>
+      <c r="D137" t="s">
+        <v>263</v>
+      </c>
+      <c r="E137" t="s">
+        <v>830</v>
+      </c>
+      <c r="F137" t="s">
+        <v>831</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>833</v>
+      </c>
+      <c r="B138" t="s">
+        <v>834</v>
+      </c>
+      <c r="C138" t="s">
+        <v>186</v>
+      </c>
+      <c r="D138" t="s">
+        <v>201</v>
+      </c>
+      <c r="E138" t="s">
+        <v>835</v>
+      </c>
+      <c r="F138" t="s">
+        <v>836</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>838</v>
+      </c>
+      <c r="B139" t="s">
+        <v>839</v>
+      </c>
+      <c r="C139" t="s">
+        <v>222</v>
+      </c>
+      <c r="D139" t="s">
+        <v>201</v>
+      </c>
+      <c r="E139" t="s">
+        <v>840</v>
+      </c>
+      <c r="F139" t="s">
+        <v>841</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>843</v>
+      </c>
+      <c r="B140" t="s">
+        <v>844</v>
+      </c>
+      <c r="C140" t="s">
+        <v>222</v>
+      </c>
+      <c r="D140" t="s">
+        <v>201</v>
+      </c>
+      <c r="E140" t="s">
+        <v>417</v>
+      </c>
+      <c r="F140" t="s">
+        <v>333</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>846</v>
+      </c>
+      <c r="B141" t="s">
+        <v>847</v>
+      </c>
+      <c r="C141" t="s">
+        <v>848</v>
+      </c>
+      <c r="D141" t="s">
+        <v>201</v>
+      </c>
+      <c r="E141" t="s">
+        <v>849</v>
+      </c>
+      <c r="F141" t="s">
+        <v>850</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>852</v>
+      </c>
+      <c r="B142" t="s">
+        <v>853</v>
+      </c>
+      <c r="C142" t="s">
+        <v>353</v>
+      </c>
+      <c r="D142" t="s">
+        <v>201</v>
+      </c>
+      <c r="E142" t="s">
+        <v>854</v>
+      </c>
+      <c r="F142" t="s">
+        <v>253</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>856</v>
+      </c>
+      <c r="B143" t="s">
+        <v>857</v>
+      </c>
+      <c r="C143" t="s">
+        <v>222</v>
+      </c>
+      <c r="D143" t="s">
+        <v>201</v>
+      </c>
+      <c r="E143" t="s">
+        <v>858</v>
+      </c>
+      <c r="F143" t="s">
+        <v>210</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -3080,6 +7703,116 @@
     <hyperlink ref="H31" r:id="rId30"/>
     <hyperlink ref="H32" r:id="rId31"/>
     <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3088,7 +7821,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3127,8 +7860,1021 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2" t="s">
+        <v>862</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>863</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>865</v>
+      </c>
+      <c r="B3" t="s">
+        <v>866</v>
+      </c>
+      <c r="C3" t="s">
+        <v>867</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" t="s">
+        <v>863</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>869</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>870</v>
+      </c>
+      <c r="D4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" t="s">
+        <v>871</v>
+      </c>
+      <c r="G4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>873</v>
+      </c>
+      <c r="B5" t="s">
+        <v>874</v>
+      </c>
+      <c r="C5" t="s">
+        <v>875</v>
+      </c>
+      <c r="D5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" t="s">
+        <v>876</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>878</v>
+      </c>
+      <c r="B6" t="s">
+        <v>879</v>
+      </c>
+      <c r="C6" t="s">
+        <v>880</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" t="s">
+        <v>871</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>882</v>
+      </c>
+      <c r="B7" t="s">
+        <v>883</v>
+      </c>
+      <c r="C7" t="s">
+        <v>884</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" t="s">
+        <v>885</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>887</v>
+      </c>
+      <c r="B8" t="s">
+        <v>888</v>
+      </c>
+      <c r="C8" t="s">
+        <v>889</v>
+      </c>
+      <c r="D8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" t="s">
+        <v>871</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B9" t="s">
+        <v>892</v>
+      </c>
+      <c r="C9" t="s">
+        <v>604</v>
+      </c>
+      <c r="D9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" t="s">
+        <v>871</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>894</v>
+      </c>
+      <c r="B10" t="s">
+        <v>895</v>
+      </c>
+      <c r="C10" t="s">
+        <v>896</v>
+      </c>
+      <c r="D10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" t="s">
+        <v>871</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>898</v>
+      </c>
+      <c r="B11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C11" t="s">
+        <v>900</v>
+      </c>
+      <c r="D11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" t="s">
+        <v>885</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>902</v>
+      </c>
+      <c r="B12" t="s">
+        <v>903</v>
+      </c>
+      <c r="C12" t="s">
+        <v>904</v>
+      </c>
+      <c r="D12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" t="s">
+        <v>871</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>906</v>
+      </c>
+      <c r="B13" t="s">
+        <v>874</v>
+      </c>
+      <c r="C13" t="s">
+        <v>875</v>
+      </c>
+      <c r="D13" t="s">
+        <v>253</v>
+      </c>
+      <c r="E13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>876</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>908</v>
+      </c>
+      <c r="B14" t="s">
+        <v>909</v>
+      </c>
+      <c r="C14" t="s">
+        <v>910</v>
+      </c>
+      <c r="D14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
+        <v>876</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>912</v>
+      </c>
+      <c r="B15" t="s">
+        <v>913</v>
+      </c>
+      <c r="C15" t="s">
+        <v>914</v>
+      </c>
+      <c r="D15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" t="s">
+        <v>253</v>
+      </c>
+      <c r="F15" t="s">
+        <v>871</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>916</v>
+      </c>
+      <c r="B16" t="s">
+        <v>874</v>
+      </c>
+      <c r="C16" t="s">
+        <v>875</v>
+      </c>
+      <c r="D16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" t="s">
+        <v>253</v>
+      </c>
+      <c r="F16" t="s">
+        <v>871</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>918</v>
+      </c>
+      <c r="B17" t="s">
+        <v>919</v>
+      </c>
+      <c r="C17" t="s">
+        <v>920</v>
+      </c>
+      <c r="D17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" t="s">
+        <v>863</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>922</v>
+      </c>
+      <c r="B18" t="s">
+        <v>923</v>
+      </c>
+      <c r="C18" t="s">
+        <v>924</v>
+      </c>
+      <c r="D18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" t="s">
+        <v>483</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>922</v>
+      </c>
+      <c r="B19" t="s">
+        <v>926</v>
+      </c>
+      <c r="C19" t="s">
+        <v>927</v>
+      </c>
+      <c r="D19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" t="s">
+        <v>871</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>929</v>
+      </c>
+      <c r="B20" t="s">
+        <v>930</v>
+      </c>
+      <c r="C20" t="s">
+        <v>927</v>
+      </c>
+      <c r="D20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" t="s">
+        <v>253</v>
+      </c>
+      <c r="F20" t="s">
+        <v>871</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>929</v>
+      </c>
+      <c r="B21" t="s">
+        <v>932</v>
+      </c>
+      <c r="C21" t="s">
+        <v>933</v>
+      </c>
+      <c r="D21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" t="s">
+        <v>871</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>935</v>
+      </c>
+      <c r="B22" t="s">
+        <v>936</v>
+      </c>
+      <c r="C22" t="s">
+        <v>937</v>
+      </c>
+      <c r="D22" t="s">
+        <v>253</v>
+      </c>
+      <c r="E22" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" t="s">
+        <v>871</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>935</v>
+      </c>
+      <c r="B23" t="s">
+        <v>939</v>
+      </c>
+      <c r="C23" t="s">
+        <v>940</v>
+      </c>
+      <c r="D23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" t="s">
+        <v>871</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>935</v>
+      </c>
+      <c r="B24" t="s">
+        <v>942</v>
+      </c>
+      <c r="C24" t="s">
+        <v>943</v>
+      </c>
+      <c r="D24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" t="s">
+        <v>253</v>
+      </c>
+      <c r="F24" t="s">
+        <v>871</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>945</v>
+      </c>
+      <c r="B25" t="s">
+        <v>946</v>
+      </c>
+      <c r="C25" t="s">
+        <v>947</v>
+      </c>
+      <c r="D25" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F25" t="s">
+        <v>871</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>949</v>
+      </c>
+      <c r="B26" t="s">
+        <v>950</v>
+      </c>
+      <c r="C26" t="s">
+        <v>604</v>
+      </c>
+      <c r="D26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F26" t="s">
+        <v>871</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>952</v>
+      </c>
+      <c r="B27" t="s">
+        <v>953</v>
+      </c>
+      <c r="C27" t="s">
+        <v>954</v>
+      </c>
+      <c r="D27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F27" t="s">
+        <v>885</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>956</v>
+      </c>
+      <c r="B28" t="s">
+        <v>957</v>
+      </c>
+      <c r="C28" t="s">
+        <v>958</v>
+      </c>
+      <c r="D28" t="s">
+        <v>253</v>
+      </c>
+      <c r="E28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F28" t="s">
+        <v>871</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>960</v>
+      </c>
+      <c r="B29" t="s">
+        <v>961</v>
+      </c>
+      <c r="C29" t="s">
+        <v>962</v>
+      </c>
+      <c r="D29" t="s">
+        <v>253</v>
+      </c>
+      <c r="E29" t="s">
+        <v>253</v>
+      </c>
+      <c r="F29" t="s">
+        <v>876</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>960</v>
+      </c>
+      <c r="B30" t="s">
+        <v>961</v>
+      </c>
+      <c r="C30" t="s">
+        <v>962</v>
+      </c>
+      <c r="D30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" t="s">
+        <v>876</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>965</v>
+      </c>
+      <c r="B31" t="s">
+        <v>966</v>
+      </c>
+      <c r="C31" t="s">
+        <v>967</v>
+      </c>
+      <c r="D31" t="s">
+        <v>253</v>
+      </c>
+      <c r="E31" t="s">
+        <v>253</v>
+      </c>
+      <c r="F31" t="s">
+        <v>871</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>969</v>
+      </c>
+      <c r="B32" t="s">
+        <v>970</v>
+      </c>
+      <c r="C32" t="s">
+        <v>947</v>
+      </c>
+      <c r="D32" t="s">
+        <v>253</v>
+      </c>
+      <c r="E32" t="s">
+        <v>253</v>
+      </c>
+      <c r="F32" t="s">
+        <v>871</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>972</v>
+      </c>
+      <c r="B33" t="s">
+        <v>895</v>
+      </c>
+      <c r="C33" t="s">
+        <v>914</v>
+      </c>
+      <c r="D33" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" t="s">
+        <v>253</v>
+      </c>
+      <c r="F33" t="s">
+        <v>885</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>974</v>
+      </c>
+      <c r="B34" t="s">
+        <v>975</v>
+      </c>
+      <c r="C34" t="s">
+        <v>976</v>
+      </c>
+      <c r="D34" t="s">
+        <v>253</v>
+      </c>
+      <c r="E34" t="s">
+        <v>253</v>
+      </c>
+      <c r="F34" t="s">
+        <v>863</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>978</v>
+      </c>
+      <c r="B35" t="s">
+        <v>979</v>
+      </c>
+      <c r="C35" t="s">
+        <v>980</v>
+      </c>
+      <c r="D35" t="s">
+        <v>253</v>
+      </c>
+      <c r="E35" t="s">
+        <v>253</v>
+      </c>
+      <c r="F35" t="s">
+        <v>863</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>982</v>
+      </c>
+      <c r="B36" t="s">
+        <v>983</v>
+      </c>
+      <c r="C36" t="s">
+        <v>984</v>
+      </c>
+      <c r="D36" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" t="s">
+        <v>985</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>987</v>
+      </c>
+      <c r="B37" t="s">
+        <v>988</v>
+      </c>
+      <c r="C37" t="s">
+        <v>989</v>
+      </c>
+      <c r="D37" t="s">
+        <v>253</v>
+      </c>
+      <c r="E37" t="s">
+        <v>253</v>
+      </c>
+      <c r="F37" t="s">
+        <v>871</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>987</v>
+      </c>
+      <c r="B38" t="s">
+        <v>988</v>
+      </c>
+      <c r="C38" t="s">
+        <v>989</v>
+      </c>
+      <c r="D38" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" t="s">
+        <v>253</v>
+      </c>
+      <c r="F38" t="s">
+        <v>871</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>992</v>
+      </c>
+      <c r="B39" t="s">
+        <v>993</v>
+      </c>
+      <c r="C39" t="s">
+        <v>994</v>
+      </c>
+      <c r="D39" t="s">
+        <v>253</v>
+      </c>
+      <c r="E39" t="s">
+        <v>253</v>
+      </c>
+      <c r="F39" t="s">
+        <v>876</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>996</v>
+      </c>
+      <c r="B40" t="s">
+        <v>997</v>
+      </c>
+      <c r="C40" t="s">
+        <v>411</v>
+      </c>
+      <c r="D40" t="s">
+        <v>253</v>
+      </c>
+      <c r="E40" t="s">
+        <v>253</v>
+      </c>
+      <c r="F40" t="s">
+        <v>871</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>999</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>870</v>
+      </c>
+      <c r="D41" t="s">
+        <v>253</v>
+      </c>
+      <c r="E41" t="s">
+        <v>253</v>
+      </c>
+      <c r="F41" t="s">
+        <v>871</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D42" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" t="s">
+        <v>253</v>
+      </c>
+      <c r="F42" t="s">
+        <v>985</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D43" t="s">
+        <v>253</v>
+      </c>
+      <c r="E43" t="s">
+        <v>253</v>
+      </c>
+      <c r="F43" t="s">
+        <v>871</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>1008</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-08-25.xlsx
+++ b/docs/xlsx/jobs-2026-08-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1027">
   <si>
     <t>Title</t>
   </si>
@@ -1054,6 +1054,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5f589a5cca024eb39a8425b3232ece70-communications-coordinator-national-youth-employment-coalition-washington</t>
   </si>
   <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Carolina for Kibera, INC.</t>
+  </si>
+  <si>
+    <t>Chapel Hill, NC</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28358e4ec7c9473a96f43a5eeeb2e76d-communications-manager-carolina-for-kibera-inc-chapel-hill</t>
+  </si>
+  <si>
     <t>Community Canvasser</t>
   </si>
   <si>
@@ -2416,9 +2431,6 @@
     <t>Staff Accountant</t>
   </si>
   <si>
-    <t>USD 70000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d5ab3ce72792413386052e8e014a8e62-staff-accountant-unite-america-denver</t>
   </si>
   <si>
@@ -2782,6 +2794,9 @@
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72580369</t>
   </si>
   <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72617029</t>
+  </si>
+  <si>
     <t>EXTENSION EDUCATOR</t>
   </si>
   <si>
@@ -2962,6 +2977,33 @@
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72582813</t>
   </si>
   <si>
+    <t>POST DOCTORAL ASSOCIATE</t>
+  </si>
+  <si>
+    <t>RURAL ECONOMIC RESILIENCE AND FOOD SYSTEMS - University of Vermont</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72615807</t>
+  </si>
+  <si>
+    <t>PRESIDENT AND CEO</t>
+  </si>
+  <si>
+    <t>Farm Foundation</t>
+  </si>
+  <si>
+    <t>Chicagoland or Remote, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72618251</t>
+  </si>
+  <si>
     <t>PROGRAM OFFICER</t>
   </si>
   <si>
@@ -3041,6 +3083,18 @@
   </si>
   <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72602365</t>
+  </si>
+  <si>
+    <t>URBAN GARDENER</t>
+  </si>
+  <si>
+    <t>Love and Carrots</t>
+  </si>
+  <si>
+    <t>Across DC, MD, and VA, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72614585</t>
   </si>
 </sst>
 </file>
@@ -4354,7 +4408,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5074,13 +5128,13 @@
         <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
+        <v>349</v>
       </c>
       <c r="F31" t="s">
-        <v>349</v>
+        <v>230</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>350</v>
@@ -5097,47 +5151,47 @@
         <v>353</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E32" t="s">
+        <v>218</v>
+      </c>
+      <c r="F32" t="s">
         <v>354</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>356</v>
+      </c>
+      <c r="B33" t="s">
         <v>357</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>358</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" t="s">
         <v>359</v>
       </c>
-      <c r="D33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>360</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>362</v>
+      </c>
+      <c r="B34" t="s">
         <v>363</v>
-      </c>
-      <c r="B34" t="s">
-        <v>302</v>
       </c>
       <c r="C34" t="s">
         <v>364</v>
@@ -5146,24 +5200,24 @@
         <v>201</v>
       </c>
       <c r="E34" t="s">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="F34" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s">
         <v>302</v>
       </c>
       <c r="C35" t="s">
-        <v>303</v>
+        <v>369</v>
       </c>
       <c r="D35" t="s">
         <v>201</v>
@@ -5175,41 +5229,41 @@
         <v>305</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="C36" t="s">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="D36" t="s">
         <v>201</v>
       </c>
       <c r="E36" t="s">
-        <v>369</v>
+        <v>304</v>
       </c>
       <c r="F36" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C37" t="s">
-        <v>373</v>
+        <v>186</v>
       </c>
       <c r="D37" t="s">
         <v>201</v>
@@ -5218,32 +5272,29 @@
         <v>374</v>
       </c>
       <c r="F37" t="s">
+        <v>242</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" t="s">
         <v>377</v>
       </c>
-      <c r="B38" t="s">
-        <v>185</v>
-      </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="E38" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F38" t="s">
-        <v>379</v>
-      </c>
-      <c r="G38" t="s">
         <v>380</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -5255,18 +5306,21 @@
         <v>382</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>185</v>
       </c>
       <c r="C39" t="s">
         <v>186</v>
       </c>
       <c r="D39" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="E39" t="s">
+        <v>383</v>
+      </c>
+      <c r="F39" t="s">
         <v>384</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>385</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -5281,7 +5335,7 @@
         <v>388</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s">
         <v>201</v>
@@ -5290,41 +5344,41 @@
         <v>389</v>
       </c>
       <c r="F40" t="s">
-        <v>253</v>
+        <v>390</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="D41" t="s">
         <v>201</v>
       </c>
       <c r="E41" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F41" t="s">
-        <v>393</v>
+        <v>253</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C42" t="s">
         <v>284</v>
@@ -5333,24 +5387,24 @@
         <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F42" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B43" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C43" t="s">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="D43" t="s">
         <v>201</v>
@@ -5359,38 +5413,38 @@
         <v>401</v>
       </c>
       <c r="F43" t="s">
+        <v>398</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>403</v>
+      </c>
+      <c r="B44" t="s">
         <v>404</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>405</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" t="s">
         <v>406</v>
       </c>
-      <c r="D44" t="s">
-        <v>201</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>407</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s">
         <v>410</v>
@@ -5413,13 +5467,13 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>409</v>
+      </c>
+      <c r="B46" t="s">
         <v>415</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>416</v>
-      </c>
-      <c r="C46" t="s">
-        <v>222</v>
       </c>
       <c r="D46" t="s">
         <v>201</v>
@@ -5465,7 +5519,7 @@
         <v>426</v>
       </c>
       <c r="C48" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D48" t="s">
         <v>201</v>
@@ -5488,7 +5542,7 @@
         <v>431</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D49" t="s">
         <v>201</v>
@@ -5557,7 +5611,7 @@
         <v>446</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="D52" t="s">
         <v>201</v>
@@ -5580,108 +5634,108 @@
         <v>451</v>
       </c>
       <c r="C53" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" t="s">
+        <v>201</v>
+      </c>
+      <c r="E53" t="s">
         <v>452</v>
       </c>
-      <c r="D53" t="s">
-        <v>201</v>
-      </c>
-      <c r="E53" t="s">
-        <v>290</v>
-      </c>
       <c r="F53" t="s">
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C54" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D54" t="s">
         <v>201</v>
       </c>
       <c r="E54" t="s">
-        <v>457</v>
+        <v>290</v>
       </c>
       <c r="F54" t="s">
+        <v>253</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>459</v>
+      </c>
+      <c r="B55" t="s">
         <v>460</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>461</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" t="s">
         <v>462</v>
       </c>
-      <c r="D55" t="s">
-        <v>201</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>463</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>465</v>
+      </c>
+      <c r="B56" t="s">
         <v>466</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>467</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" t="s">
         <v>468</v>
       </c>
-      <c r="D56" t="s">
-        <v>201</v>
-      </c>
-      <c r="E56" t="s">
-        <v>253</v>
-      </c>
       <c r="F56" t="s">
-        <v>253</v>
+        <v>469</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C57" t="s">
-        <v>222</v>
+        <v>473</v>
       </c>
       <c r="D57" t="s">
         <v>201</v>
       </c>
       <c r="E57" t="s">
-        <v>472</v>
+        <v>253</v>
       </c>
       <c r="F57" t="s">
-        <v>473</v>
+        <v>253</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>474</v>
@@ -5695,7 +5749,7 @@
         <v>476</v>
       </c>
       <c r="C58" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="D58" t="s">
         <v>201</v>
@@ -5718,7 +5772,7 @@
         <v>481</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>284</v>
       </c>
       <c r="D59" t="s">
         <v>201</v>
@@ -5741,30 +5795,30 @@
         <v>486</v>
       </c>
       <c r="C60" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" t="s">
+        <v>201</v>
+      </c>
+      <c r="E60" t="s">
         <v>487</v>
       </c>
-      <c r="D60" t="s">
-        <v>201</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>488</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>490</v>
+      </c>
+      <c r="B61" t="s">
         <v>491</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>492</v>
-      </c>
-      <c r="C61" t="s">
-        <v>222</v>
       </c>
       <c r="D61" t="s">
         <v>201</v>
@@ -5773,38 +5827,38 @@
         <v>493</v>
       </c>
       <c r="F61" t="s">
-        <v>339</v>
+        <v>494</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s">
-        <v>319</v>
+        <v>497</v>
       </c>
       <c r="C62" t="s">
-        <v>320</v>
+        <v>222</v>
       </c>
       <c r="D62" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E62" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F62" t="s">
-        <v>253</v>
+        <v>339</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B63" t="s">
         <v>319</v>
@@ -5813,27 +5867,27 @@
         <v>320</v>
       </c>
       <c r="D63" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E63" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F63" t="s">
         <v>253</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>502</v>
+        <v>319</v>
       </c>
       <c r="C64" t="s">
-        <v>503</v>
+        <v>320</v>
       </c>
       <c r="D64" t="s">
         <v>201</v>
@@ -5842,27 +5896,27 @@
         <v>504</v>
       </c>
       <c r="F64" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>506</v>
+      </c>
+      <c r="B65" t="s">
         <v>507</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>508</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" t="s">
         <v>509</v>
-      </c>
-      <c r="D65" t="s">
-        <v>201</v>
-      </c>
-      <c r="E65" t="s">
-        <v>396</v>
       </c>
       <c r="F65" t="s">
         <v>510</v>
@@ -5873,25 +5927,25 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C66" t="s">
-        <v>284</v>
+        <v>514</v>
       </c>
       <c r="D66" t="s">
         <v>201</v>
       </c>
       <c r="E66" t="s">
-        <v>513</v>
+        <v>401</v>
       </c>
       <c r="F66" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -5899,10 +5953,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C67" t="s">
-        <v>517</v>
+        <v>284</v>
       </c>
       <c r="D67" t="s">
         <v>201</v>
@@ -5911,15 +5965,15 @@
         <v>518</v>
       </c>
       <c r="F67" t="s">
-        <v>253</v>
+        <v>519</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>520</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
         <v>521</v>
@@ -5934,73 +5988,73 @@
         <v>523</v>
       </c>
       <c r="F68" t="s">
+        <v>253</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s">
         <v>526</v>
       </c>
       <c r="C69" t="s">
-        <v>487</v>
+        <v>527</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>528</v>
       </c>
       <c r="F69" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C70" t="s">
-        <v>222</v>
+        <v>492</v>
       </c>
       <c r="D70" t="s">
         <v>201</v>
       </c>
       <c r="E70" t="s">
-        <v>530</v>
+        <v>253</v>
       </c>
       <c r="F70" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s">
         <v>534</v>
       </c>
       <c r="C71" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" t="s">
         <v>535</v>
-      </c>
-      <c r="D71" t="s">
-        <v>208</v>
-      </c>
-      <c r="E71" t="s">
-        <v>290</v>
       </c>
       <c r="F71" t="s">
         <v>536</v>
@@ -6020,10 +6074,10 @@
         <v>540</v>
       </c>
       <c r="D72" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E72" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F72" t="s">
         <v>541</v>
@@ -6043,102 +6097,102 @@
         <v>545</v>
       </c>
       <c r="D73" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E73" t="s">
+        <v>285</v>
+      </c>
+      <c r="F73" t="s">
         <v>546</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>548</v>
+      </c>
+      <c r="B74" t="s">
         <v>549</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>550</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>208</v>
+      </c>
+      <c r="E74" t="s">
         <v>551</v>
       </c>
-      <c r="D74" t="s">
-        <v>234</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>552</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>554</v>
+      </c>
+      <c r="B75" t="s">
         <v>555</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>556</v>
       </c>
-      <c r="C75" t="s">
-        <v>373</v>
-      </c>
       <c r="D75" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="E75" t="s">
         <v>557</v>
       </c>
       <c r="F75" t="s">
-        <v>379</v>
+        <v>558</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C76" t="s">
-        <v>284</v>
+        <v>378</v>
       </c>
       <c r="D76" t="s">
         <v>201</v>
       </c>
       <c r="E76" t="s">
-        <v>417</v>
+        <v>562</v>
       </c>
       <c r="F76" t="s">
-        <v>561</v>
+        <v>384</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B77" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C77" t="s">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="D77" t="s">
         <v>201</v>
       </c>
       <c r="E77" t="s">
-        <v>565</v>
+        <v>422</v>
       </c>
       <c r="F77" t="s">
         <v>566</v>
@@ -6155,70 +6209,70 @@
         <v>569</v>
       </c>
       <c r="C78" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" t="s">
+        <v>201</v>
+      </c>
+      <c r="E78" t="s">
         <v>570</v>
       </c>
-      <c r="D78" t="s">
-        <v>208</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>571</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>573</v>
+      </c>
+      <c r="B79" t="s">
         <v>574</v>
       </c>
-      <c r="B79" t="s">
-        <v>206</v>
-      </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>575</v>
       </c>
       <c r="D79" t="s">
         <v>208</v>
       </c>
       <c r="E79" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F79" t="s">
-        <v>210</v>
+        <v>577</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B80" t="s">
         <v>206</v>
       </c>
       <c r="C80" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D80" t="s">
         <v>208</v>
       </c>
       <c r="E80" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F80" t="s">
         <v>210</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B81" t="s">
         <v>206</v>
@@ -6230,13 +6284,13 @@
         <v>208</v>
       </c>
       <c r="E81" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="F81" t="s">
         <v>210</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -6244,79 +6298,79 @@
         <v>579</v>
       </c>
       <c r="B82" t="s">
+        <v>206</v>
+      </c>
+      <c r="C82" t="s">
+        <v>207</v>
+      </c>
+      <c r="D82" t="s">
+        <v>208</v>
+      </c>
+      <c r="E82" t="s">
         <v>580</v>
       </c>
-      <c r="C82" t="s">
-        <v>581</v>
-      </c>
-      <c r="D82" t="s">
-        <v>201</v>
-      </c>
-      <c r="E82" t="s">
-        <v>582</v>
-      </c>
       <c r="F82" t="s">
+        <v>210</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>584</v>
+      </c>
+      <c r="B83" t="s">
         <v>585</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>586</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>201</v>
+      </c>
+      <c r="E83" t="s">
         <v>587</v>
       </c>
-      <c r="D83" t="s">
-        <v>208</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>588</v>
       </c>
-      <c r="F83" t="s">
+      <c r="H83" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>590</v>
+      </c>
+      <c r="B84" t="s">
         <v>591</v>
       </c>
-      <c r="B84" t="s">
-        <v>392</v>
-      </c>
       <c r="C84" t="s">
-        <v>222</v>
+        <v>592</v>
       </c>
       <c r="D84" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E84" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F84" t="s">
-        <v>393</v>
+        <v>594</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B85" t="s">
-        <v>595</v>
+        <v>397</v>
       </c>
       <c r="C85" t="s">
-        <v>596</v>
+        <v>222</v>
       </c>
       <c r="D85" t="s">
         <v>201</v>
@@ -6325,67 +6379,67 @@
         <v>597</v>
       </c>
       <c r="F85" t="s">
+        <v>398</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B86" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C86" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D86" t="s">
         <v>201</v>
       </c>
       <c r="E86" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F86" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>599</v>
+      </c>
+      <c r="B87" t="s">
+        <v>600</v>
+      </c>
+      <c r="C87" t="s">
+        <v>605</v>
+      </c>
+      <c r="D87" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" t="s">
         <v>602</v>
       </c>
-      <c r="B87" t="s">
+      <c r="F87" t="s">
         <v>603</v>
       </c>
-      <c r="C87" t="s">
-        <v>604</v>
-      </c>
-      <c r="D87" t="s">
-        <v>201</v>
-      </c>
-      <c r="E87" t="s">
-        <v>605</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="H87" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>607</v>
+      </c>
+      <c r="B88" t="s">
         <v>608</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>609</v>
-      </c>
-      <c r="C88" t="s">
-        <v>186</v>
       </c>
       <c r="D88" t="s">
         <v>201</v>
@@ -6408,16 +6462,16 @@
         <v>614</v>
       </c>
       <c r="C89" t="s">
+        <v>186</v>
+      </c>
+      <c r="D89" t="s">
+        <v>201</v>
+      </c>
+      <c r="E89" t="s">
         <v>615</v>
       </c>
-      <c r="D89" t="s">
-        <v>201</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>616</v>
-      </c>
-      <c r="F89" t="s">
-        <v>236</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>617</v>
@@ -6434,96 +6488,96 @@
         <v>620</v>
       </c>
       <c r="D90" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E90" t="s">
         <v>621</v>
       </c>
       <c r="F90" t="s">
+        <v>236</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>623</v>
+      </c>
+      <c r="B91" t="s">
         <v>624</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>625</v>
       </c>
-      <c r="C91" t="s">
-        <v>320</v>
-      </c>
       <c r="D91" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="E91" t="s">
-        <v>523</v>
+        <v>626</v>
       </c>
       <c r="F91" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B92" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C92" t="s">
-        <v>630</v>
+        <v>320</v>
       </c>
       <c r="D92" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="E92" t="s">
+        <v>528</v>
+      </c>
+      <c r="F92" t="s">
         <v>631</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>633</v>
+      </c>
+      <c r="B93" t="s">
         <v>634</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>635</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" t="s">
         <v>636</v>
       </c>
-      <c r="D93" t="s">
-        <v>201</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>637</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>639</v>
+      </c>
+      <c r="B94" t="s">
         <v>640</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>641</v>
-      </c>
-      <c r="C94" t="s">
-        <v>615</v>
       </c>
       <c r="D94" t="s">
         <v>201</v>
@@ -6532,53 +6586,53 @@
         <v>642</v>
       </c>
       <c r="F94" t="s">
-        <v>402</v>
+        <v>643</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B95" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C95" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D95" t="s">
         <v>201</v>
       </c>
       <c r="E95" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="F95" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>649</v>
+      </c>
+      <c r="B96" t="s">
         <v>646</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>620</v>
+      </c>
+      <c r="D96" t="s">
+        <v>201</v>
+      </c>
+      <c r="E96" t="s">
         <v>647</v>
       </c>
-      <c r="C96" t="s">
-        <v>314</v>
-      </c>
-      <c r="D96" t="s">
-        <v>201</v>
-      </c>
-      <c r="E96" t="s">
-        <v>648</v>
-      </c>
       <c r="F96" t="s">
-        <v>649</v>
+        <v>407</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>650</v>
@@ -6592,7 +6646,7 @@
         <v>652</v>
       </c>
       <c r="C97" t="s">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="D97" t="s">
         <v>201</v>
@@ -6615,85 +6669,85 @@
         <v>657</v>
       </c>
       <c r="C98" t="s">
-        <v>359</v>
+        <v>186</v>
       </c>
       <c r="D98" t="s">
         <v>201</v>
       </c>
       <c r="E98" t="s">
-        <v>253</v>
+        <v>658</v>
       </c>
       <c r="F98" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B99" t="s">
-        <v>330</v>
+        <v>662</v>
       </c>
       <c r="C99" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="D99" t="s">
         <v>201</v>
       </c>
       <c r="E99" t="s">
-        <v>661</v>
+        <v>253</v>
       </c>
       <c r="F99" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B100" t="s">
-        <v>665</v>
+        <v>330</v>
       </c>
       <c r="C100" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D100" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E100" t="s">
         <v>666</v>
       </c>
       <c r="F100" t="s">
-        <v>210</v>
+        <v>667</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B101" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C101" t="s">
-        <v>186</v>
+        <v>320</v>
       </c>
       <c r="D101" t="s">
         <v>208</v>
       </c>
       <c r="E101" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F101" t="s">
-        <v>671</v>
+        <v>210</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>672</v>
@@ -6707,39 +6761,39 @@
         <v>674</v>
       </c>
       <c r="C102" t="s">
+        <v>186</v>
+      </c>
+      <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
         <v>675</v>
       </c>
-      <c r="D102" t="s">
-        <v>201</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>676</v>
       </c>
-      <c r="F102" t="s">
+      <c r="H102" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>678</v>
+      </c>
+      <c r="B103" t="s">
         <v>679</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>680</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>201</v>
+      </c>
+      <c r="E103" t="s">
         <v>681</v>
       </c>
-      <c r="D103" t="s">
-        <v>201</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>682</v>
-      </c>
-      <c r="F103" t="s">
-        <v>253</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>683</v>
@@ -6750,42 +6804,42 @@
         <v>684</v>
       </c>
       <c r="B104" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C104" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D104" t="s">
         <v>201</v>
       </c>
       <c r="E104" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F104" t="s">
         <v>253</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>689</v>
+      </c>
+      <c r="B105" t="s">
+        <v>685</v>
+      </c>
+      <c r="C105" t="s">
+        <v>690</v>
+      </c>
+      <c r="D105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E105" t="s">
         <v>687</v>
       </c>
-      <c r="B105" t="s">
-        <v>688</v>
-      </c>
-      <c r="C105" t="s">
-        <v>689</v>
-      </c>
-      <c r="D105" t="s">
-        <v>234</v>
-      </c>
-      <c r="E105" t="s">
-        <v>253</v>
-      </c>
       <c r="F105" t="s">
-        <v>690</v>
+        <v>253</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>691</v>
@@ -6799,76 +6853,76 @@
         <v>693</v>
       </c>
       <c r="C106" t="s">
-        <v>456</v>
+        <v>694</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="E106" t="s">
-        <v>694</v>
+        <v>253</v>
       </c>
       <c r="F106" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B107" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C107" t="s">
-        <v>698</v>
+        <v>461</v>
       </c>
       <c r="D107" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E107" t="s">
         <v>699</v>
       </c>
       <c r="F107" t="s">
+        <v>663</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>701</v>
+      </c>
+      <c r="B108" t="s">
         <v>702</v>
       </c>
-      <c r="B108" t="s">
-        <v>253</v>
-      </c>
       <c r="C108" t="s">
-        <v>456</v>
+        <v>703</v>
       </c>
       <c r="D108" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E108" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F108" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B109" t="s">
-        <v>706</v>
+        <v>253</v>
       </c>
       <c r="C109" t="s">
-        <v>707</v>
+        <v>461</v>
       </c>
       <c r="D109" t="s">
         <v>201</v>
@@ -6877,27 +6931,27 @@
         <v>708</v>
       </c>
       <c r="F109" t="s">
+        <v>695</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>710</v>
+      </c>
+      <c r="B110" t="s">
         <v>711</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>712</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>201</v>
+      </c>
+      <c r="E110" t="s">
         <v>713</v>
-      </c>
-      <c r="D110" t="s">
-        <v>246</v>
-      </c>
-      <c r="E110" t="s">
-        <v>670</v>
       </c>
       <c r="F110" t="s">
         <v>714</v>
@@ -6911,30 +6965,30 @@
         <v>716</v>
       </c>
       <c r="B111" t="s">
-        <v>272</v>
+        <v>717</v>
       </c>
       <c r="C111" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D111" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="E111" t="s">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="F111" t="s">
-        <v>230</v>
+        <v>719</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B112" t="s">
-        <v>721</v>
+        <v>272</v>
       </c>
       <c r="C112" t="s">
         <v>722</v>
@@ -6943,79 +6997,79 @@
         <v>201</v>
       </c>
       <c r="E112" t="s">
-        <v>253</v>
+        <v>723</v>
       </c>
       <c r="F112" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B113" t="s">
-        <v>272</v>
+        <v>726</v>
       </c>
       <c r="C113" t="s">
-        <v>273</v>
+        <v>727</v>
       </c>
       <c r="D113" t="s">
         <v>201</v>
       </c>
       <c r="E113" t="s">
-        <v>725</v>
+        <v>253</v>
       </c>
       <c r="F113" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>143</v>
+        <v>729</v>
       </c>
       <c r="B114" t="s">
-        <v>392</v>
+        <v>272</v>
       </c>
       <c r="C114" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="D114" t="s">
-        <v>246</v>
+        <v>201</v>
       </c>
       <c r="E114" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="F114" t="s">
-        <v>393</v>
+        <v>230</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>729</v>
+        <v>143</v>
       </c>
       <c r="B115" t="s">
-        <v>730</v>
+        <v>397</v>
       </c>
       <c r="C115" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D115" t="s">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="E115" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F115" t="s">
-        <v>732</v>
+        <v>398</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>733</v>
@@ -7026,10 +7080,10 @@
         <v>734</v>
       </c>
       <c r="B116" t="s">
-        <v>272</v>
+        <v>735</v>
       </c>
       <c r="C116" t="s">
-        <v>735</v>
+        <v>186</v>
       </c>
       <c r="D116" t="s">
         <v>201</v>
@@ -7038,76 +7092,76 @@
         <v>736</v>
       </c>
       <c r="F116" t="s">
-        <v>230</v>
+        <v>737</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B117" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>740</v>
       </c>
       <c r="D117" t="s">
         <v>201</v>
       </c>
       <c r="E117" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F117" t="s">
-        <v>349</v>
+        <v>230</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B118" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C118" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D118" t="s">
         <v>201</v>
       </c>
       <c r="E118" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F118" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B119" t="s">
-        <v>614</v>
+        <v>352</v>
       </c>
       <c r="C119" t="s">
+        <v>353</v>
+      </c>
+      <c r="D119" t="s">
+        <v>201</v>
+      </c>
+      <c r="E119" t="s">
         <v>744</v>
       </c>
-      <c r="D119" t="s">
-        <v>201</v>
-      </c>
-      <c r="E119" t="s">
-        <v>745</v>
-      </c>
       <c r="F119" t="s">
-        <v>746</v>
+        <v>354</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>747</v>
@@ -7118,42 +7172,42 @@
         <v>748</v>
       </c>
       <c r="B120" t="s">
-        <v>410</v>
+        <v>619</v>
       </c>
       <c r="C120" t="s">
-        <v>411</v>
+        <v>749</v>
       </c>
       <c r="D120" t="s">
         <v>201</v>
       </c>
       <c r="E120" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F120" t="s">
-        <v>413</v>
+        <v>751</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B121" t="s">
-        <v>752</v>
+        <v>415</v>
       </c>
       <c r="C121" t="s">
-        <v>284</v>
+        <v>416</v>
       </c>
       <c r="D121" t="s">
         <v>201</v>
       </c>
       <c r="E121" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F121" t="s">
-        <v>754</v>
+        <v>418</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>755</v>
@@ -7161,88 +7215,88 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>191</v>
+        <v>756</v>
       </c>
       <c r="B122" t="s">
-        <v>185</v>
+        <v>757</v>
       </c>
       <c r="C122" t="s">
-        <v>186</v>
+        <v>284</v>
       </c>
       <c r="D122" t="s">
         <v>201</v>
       </c>
       <c r="E122" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F122" t="s">
-        <v>757</v>
-      </c>
-      <c r="G122" t="s">
-        <v>380</v>
+        <v>759</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>759</v>
+        <v>191</v>
       </c>
       <c r="B123" t="s">
-        <v>358</v>
+        <v>185</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>186</v>
       </c>
       <c r="D123" t="s">
         <v>201</v>
       </c>
       <c r="E123" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F123" t="s">
-        <v>361</v>
+        <v>762</v>
+      </c>
+      <c r="G123" t="s">
+        <v>385</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B124" t="s">
-        <v>763</v>
+        <v>363</v>
       </c>
       <c r="C124" t="s">
-        <v>764</v>
+        <v>364</v>
       </c>
       <c r="D124" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E124" t="s">
         <v>765</v>
       </c>
       <c r="F124" t="s">
+        <v>366</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>767</v>
+      </c>
+      <c r="B125" t="s">
         <v>768</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>769</v>
       </c>
-      <c r="C125" t="s">
-        <v>222</v>
-      </c>
       <c r="D125" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E125" t="s">
         <v>770</v>
@@ -7262,39 +7316,39 @@
         <v>774</v>
       </c>
       <c r="C126" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D126" t="s">
         <v>201</v>
       </c>
       <c r="E126" t="s">
-        <v>241</v>
+        <v>775</v>
       </c>
       <c r="F126" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B127" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C127" t="s">
-        <v>779</v>
+        <v>186</v>
       </c>
       <c r="D127" t="s">
         <v>201</v>
       </c>
       <c r="E127" t="s">
+        <v>241</v>
+      </c>
+      <c r="F127" t="s">
         <v>780</v>
-      </c>
-      <c r="F127" t="s">
-        <v>253</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>781</v>
@@ -7317,27 +7371,27 @@
         <v>785</v>
       </c>
       <c r="F128" t="s">
+        <v>253</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>787</v>
+      </c>
+      <c r="B129" t="s">
         <v>788</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>789</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
+        <v>201</v>
+      </c>
+      <c r="E129" t="s">
         <v>790</v>
-      </c>
-      <c r="D129" t="s">
-        <v>201</v>
-      </c>
-      <c r="E129" t="s">
-        <v>253</v>
       </c>
       <c r="F129" t="s">
         <v>791</v>
@@ -7360,79 +7414,79 @@
         <v>201</v>
       </c>
       <c r="E130" t="s">
+        <v>253</v>
+      </c>
+      <c r="F130" t="s">
         <v>796</v>
       </c>
-      <c r="F130" t="s">
+      <c r="H130" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>798</v>
+      </c>
+      <c r="B131" t="s">
         <v>799</v>
       </c>
-      <c r="B131" t="s">
-        <v>794</v>
-      </c>
       <c r="C131" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="D131" t="s">
         <v>201</v>
       </c>
       <c r="E131" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F131" t="s">
-        <v>448</v>
+        <v>802</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B132" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C132" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D132" t="s">
         <v>201</v>
       </c>
       <c r="E132" t="s">
+        <v>349</v>
+      </c>
+      <c r="F132" t="s">
+        <v>453</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="F132" t="s">
-        <v>806</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>806</v>
+      </c>
+      <c r="B133" t="s">
+        <v>807</v>
+      </c>
+      <c r="C133" t="s">
         <v>808</v>
       </c>
-      <c r="B133" t="s">
-        <v>272</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>201</v>
+      </c>
+      <c r="E133" t="s">
         <v>809</v>
       </c>
-      <c r="D133" t="s">
-        <v>201</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>810</v>
-      </c>
-      <c r="F133" t="s">
-        <v>230</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>811</v>
@@ -7466,122 +7520,122 @@
         <v>816</v>
       </c>
       <c r="B135" t="s">
+        <v>272</v>
+      </c>
+      <c r="C135" t="s">
         <v>817</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>201</v>
+      </c>
+      <c r="E135" t="s">
         <v>818</v>
       </c>
-      <c r="D135" t="s">
-        <v>201</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
+        <v>230</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="F135" t="s">
-        <v>820</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>820</v>
+      </c>
+      <c r="B136" t="s">
+        <v>821</v>
+      </c>
+      <c r="C136" t="s">
         <v>822</v>
       </c>
-      <c r="B136" t="s">
+      <c r="D136" t="s">
+        <v>201</v>
+      </c>
+      <c r="E136" t="s">
         <v>823</v>
       </c>
-      <c r="C136" t="s">
-        <v>222</v>
-      </c>
-      <c r="D136" t="s">
-        <v>234</v>
-      </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>824</v>
       </c>
-      <c r="F136" t="s">
+      <c r="H136" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>826</v>
+      </c>
+      <c r="B137" t="s">
         <v>827</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
+        <v>222</v>
+      </c>
+      <c r="D137" t="s">
+        <v>234</v>
+      </c>
+      <c r="E137" t="s">
         <v>828</v>
       </c>
-      <c r="C137" t="s">
+      <c r="F137" t="s">
         <v>829</v>
       </c>
-      <c r="D137" t="s">
-        <v>263</v>
-      </c>
-      <c r="E137" t="s">
+      <c r="H137" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="F137" t="s">
-        <v>831</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>831</v>
+      </c>
+      <c r="B138" t="s">
+        <v>832</v>
+      </c>
+      <c r="C138" t="s">
         <v>833</v>
       </c>
-      <c r="B138" t="s">
+      <c r="D138" t="s">
+        <v>263</v>
+      </c>
+      <c r="E138" t="s">
         <v>834</v>
       </c>
-      <c r="C138" t="s">
-        <v>186</v>
-      </c>
-      <c r="D138" t="s">
-        <v>201</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>835</v>
       </c>
-      <c r="F138" t="s">
+      <c r="H138" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>837</v>
+      </c>
+      <c r="B139" t="s">
         <v>838</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
+        <v>186</v>
+      </c>
+      <c r="D139" t="s">
+        <v>201</v>
+      </c>
+      <c r="E139" t="s">
         <v>839</v>
       </c>
-      <c r="C139" t="s">
-        <v>222</v>
-      </c>
-      <c r="D139" t="s">
-        <v>201</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>840</v>
       </c>
-      <c r="F139" t="s">
+      <c r="H139" s="2" t="s">
         <v>841</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>842</v>
+      </c>
+      <c r="B140" t="s">
         <v>843</v>
-      </c>
-      <c r="B140" t="s">
-        <v>844</v>
       </c>
       <c r="C140" t="s">
         <v>222</v>
@@ -7590,56 +7644,56 @@
         <v>201</v>
       </c>
       <c r="E140" t="s">
-        <v>417</v>
+        <v>844</v>
       </c>
       <c r="F140" t="s">
-        <v>333</v>
+        <v>845</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B141" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C141" t="s">
-        <v>848</v>
+        <v>222</v>
       </c>
       <c r="D141" t="s">
         <v>201</v>
       </c>
       <c r="E141" t="s">
+        <v>422</v>
+      </c>
+      <c r="F141" t="s">
+        <v>333</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="F141" t="s">
-        <v>850</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>850</v>
+      </c>
+      <c r="B142" t="s">
+        <v>851</v>
+      </c>
+      <c r="C142" t="s">
         <v>852</v>
       </c>
-      <c r="B142" t="s">
+      <c r="D142" t="s">
+        <v>201</v>
+      </c>
+      <c r="E142" t="s">
         <v>853</v>
       </c>
-      <c r="C142" t="s">
-        <v>353</v>
-      </c>
-      <c r="D142" t="s">
-        <v>201</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>854</v>
-      </c>
-      <c r="F142" t="s">
-        <v>253</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>855</v>
@@ -7653,7 +7707,7 @@
         <v>857</v>
       </c>
       <c r="C143" t="s">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="D143" t="s">
         <v>201</v>
@@ -7662,10 +7716,33 @@
         <v>858</v>
       </c>
       <c r="F143" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>859</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>860</v>
+      </c>
+      <c r="B144" t="s">
+        <v>861</v>
+      </c>
+      <c r="C144" t="s">
+        <v>222</v>
+      </c>
+      <c r="D144" t="s">
+        <v>201</v>
+      </c>
+      <c r="E144" t="s">
+        <v>862</v>
+      </c>
+      <c r="F144" t="s">
+        <v>210</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>863</v>
       </c>
     </row>
   </sheetData>
@@ -7813,6 +7890,7 @@
     <hyperlink ref="H141" r:id="rId140"/>
     <hyperlink ref="H142" r:id="rId141"/>
     <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7821,7 +7899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -7862,13 +7940,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C2" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D2" t="s">
         <v>253</v>
@@ -7877,44 +7955,44 @@
         <v>253</v>
       </c>
       <c r="F2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C3" t="s">
+        <v>871</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" t="s">
         <v>867</v>
       </c>
-      <c r="D3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F3" t="s">
-        <v>863</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D4" t="s">
         <v>253</v>
@@ -7923,24 +8001,24 @@
         <v>253</v>
       </c>
       <c r="F4" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="G4" t="s">
         <v>269</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D5" t="s">
         <v>253</v>
@@ -7949,21 +8027,21 @@
         <v>253</v>
       </c>
       <c r="F5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B6" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C6" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D6" t="s">
         <v>253</v>
@@ -7972,21 +8050,21 @@
         <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B7" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C7" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D7" t="s">
         <v>253</v>
@@ -7995,21 +8073,21 @@
         <v>253</v>
       </c>
       <c r="F7" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B8" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C8" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D8" t="s">
         <v>253</v>
@@ -8018,21 +8096,21 @@
         <v>253</v>
       </c>
       <c r="F8" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C9" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D9" t="s">
         <v>253</v>
@@ -8041,21 +8119,21 @@
         <v>253</v>
       </c>
       <c r="F9" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B10" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D10" t="s">
         <v>253</v>
@@ -8064,21 +8142,21 @@
         <v>253</v>
       </c>
       <c r="F10" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B11" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C11" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D11" t="s">
         <v>253</v>
@@ -8087,21 +8165,21 @@
         <v>253</v>
       </c>
       <c r="F11" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C12" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D12" t="s">
         <v>253</v>
@@ -8110,21 +8188,21 @@
         <v>253</v>
       </c>
       <c r="F12" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B13" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C13" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D13" t="s">
         <v>253</v>
@@ -8133,21 +8211,21 @@
         <v>253</v>
       </c>
       <c r="F13" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B14" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C14" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D14" t="s">
         <v>253</v>
@@ -8156,21 +8234,21 @@
         <v>253</v>
       </c>
       <c r="F14" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B15" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C15" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
@@ -8179,44 +8257,44 @@
         <v>253</v>
       </c>
       <c r="F15" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B16" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C16" t="s">
+        <v>879</v>
+      </c>
+      <c r="D16" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" t="s">
+        <v>253</v>
+      </c>
+      <c r="F16" t="s">
         <v>875</v>
       </c>
-      <c r="D16" t="s">
-        <v>253</v>
-      </c>
-      <c r="E16" t="s">
-        <v>253</v>
-      </c>
-      <c r="F16" t="s">
-        <v>871</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B17" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C17" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D17" t="s">
         <v>253</v>
@@ -8225,21 +8303,21 @@
         <v>253</v>
       </c>
       <c r="F17" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>922</v>
+        <v>538</v>
       </c>
       <c r="B18" t="s">
-        <v>923</v>
+        <v>857</v>
       </c>
       <c r="C18" t="s">
-        <v>924</v>
+        <v>358</v>
       </c>
       <c r="D18" t="s">
         <v>253</v>
@@ -8248,21 +8326,21 @@
         <v>253</v>
       </c>
       <c r="F18" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="B19" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D19" t="s">
         <v>253</v>
@@ -8271,21 +8349,21 @@
         <v>253</v>
       </c>
       <c r="F19" t="s">
-        <v>871</v>
+        <v>488</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B20" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C20" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="D20" t="s">
         <v>253</v>
@@ -8294,22 +8372,22 @@
         <v>253</v>
       </c>
       <c r="F20" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B21" t="s">
+        <v>935</v>
+      </c>
+      <c r="C21" t="s">
         <v>932</v>
       </c>
-      <c r="C21" t="s">
-        <v>933</v>
-      </c>
       <c r="D21" t="s">
         <v>253</v>
       </c>
@@ -8317,21 +8395,21 @@
         <v>253</v>
       </c>
       <c r="F21" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B22" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C22" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D22" t="s">
         <v>253</v>
@@ -8340,21 +8418,21 @@
         <v>253</v>
       </c>
       <c r="F22" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B23" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C23" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D23" t="s">
         <v>253</v>
@@ -8363,21 +8441,21 @@
         <v>253</v>
       </c>
       <c r="F23" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B24" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C24" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D24" t="s">
         <v>253</v>
@@ -8386,21 +8464,21 @@
         <v>253</v>
       </c>
       <c r="F24" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B25" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C25" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D25" t="s">
         <v>253</v>
@@ -8409,21 +8487,21 @@
         <v>253</v>
       </c>
       <c r="F25" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B26" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C26" t="s">
-        <v>604</v>
+        <v>952</v>
       </c>
       <c r="D26" t="s">
         <v>253</v>
@@ -8432,21 +8510,21 @@
         <v>253</v>
       </c>
       <c r="F26" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B27" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C27" t="s">
-        <v>954</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
         <v>253</v>
@@ -8455,21 +8533,21 @@
         <v>253</v>
       </c>
       <c r="F27" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B28" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C28" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D28" t="s">
         <v>253</v>
@@ -8478,21 +8556,21 @@
         <v>253</v>
       </c>
       <c r="F28" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B29" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C29" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D29" t="s">
         <v>253</v>
@@ -8501,21 +8579,21 @@
         <v>253</v>
       </c>
       <c r="F29" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="B30" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="C30" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D30" t="s">
         <v>253</v>
@@ -8524,10 +8602,10 @@
         <v>253</v>
       </c>
       <c r="F30" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -8547,21 +8625,21 @@
         <v>253</v>
       </c>
       <c r="F31" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B32" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C32" t="s">
-        <v>947</v>
+        <v>972</v>
       </c>
       <c r="D32" t="s">
         <v>253</v>
@@ -8570,21 +8648,21 @@
         <v>253</v>
       </c>
       <c r="F32" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B33" t="s">
-        <v>895</v>
+        <v>975</v>
       </c>
       <c r="C33" t="s">
-        <v>914</v>
+        <v>952</v>
       </c>
       <c r="D33" t="s">
         <v>253</v>
@@ -8593,21 +8671,21 @@
         <v>253</v>
       </c>
       <c r="F33" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B34" t="s">
-        <v>975</v>
+        <v>899</v>
       </c>
       <c r="C34" t="s">
-        <v>976</v>
+        <v>918</v>
       </c>
       <c r="D34" t="s">
         <v>253</v>
@@ -8616,21 +8694,21 @@
         <v>253</v>
       </c>
       <c r="F34" t="s">
-        <v>863</v>
+        <v>889</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B35" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C35" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D35" t="s">
         <v>253</v>
@@ -8639,21 +8717,21 @@
         <v>253</v>
       </c>
       <c r="F35" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B36" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C36" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D36" t="s">
         <v>253</v>
@@ -8662,7 +8740,7 @@
         <v>253</v>
       </c>
       <c r="F36" t="s">
-        <v>985</v>
+        <v>867</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>986</v>
@@ -8685,21 +8763,21 @@
         <v>253</v>
       </c>
       <c r="F37" t="s">
-        <v>871</v>
+        <v>990</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="B38" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="C38" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="D38" t="s">
         <v>253</v>
@@ -8708,21 +8786,21 @@
         <v>253</v>
       </c>
       <c r="F38" t="s">
-        <v>871</v>
+        <v>525</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B39" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C39" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="D39" t="s">
         <v>253</v>
@@ -8731,21 +8809,21 @@
         <v>253</v>
       </c>
       <c r="F39" t="s">
-        <v>876</v>
+        <v>999</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="B40" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="C40" t="s">
-        <v>411</v>
+        <v>1003</v>
       </c>
       <c r="D40" t="s">
         <v>253</v>
@@ -8754,21 +8832,21 @@
         <v>253</v>
       </c>
       <c r="F40" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>1002</v>
       </c>
       <c r="C41" t="s">
-        <v>870</v>
+        <v>1003</v>
       </c>
       <c r="D41" t="s">
         <v>253</v>
@@ -8777,21 +8855,21 @@
         <v>253</v>
       </c>
       <c r="F41" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="B42" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="C42" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D42" t="s">
         <v>253</v>
@@ -8800,21 +8878,21 @@
         <v>253</v>
       </c>
       <c r="F42" t="s">
-        <v>985</v>
+        <v>880</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="B43" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="C43" t="s">
-        <v>1007</v>
+        <v>416</v>
       </c>
       <c r="D43" t="s">
         <v>253</v>
@@ -8823,10 +8901,102 @@
         <v>253</v>
       </c>
       <c r="F43" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1008</v>
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>874</v>
+      </c>
+      <c r="D44" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" t="s">
+        <v>253</v>
+      </c>
+      <c r="F44" t="s">
+        <v>875</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D45" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" t="s">
+        <v>253</v>
+      </c>
+      <c r="F45" t="s">
+        <v>999</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D46" t="s">
+        <v>253</v>
+      </c>
+      <c r="E46" t="s">
+        <v>253</v>
+      </c>
+      <c r="F46" t="s">
+        <v>875</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F47" t="s">
+        <v>875</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -8874,6 +9044,10 @@
     <hyperlink ref="H41" r:id="rId40"/>
     <hyperlink ref="H42" r:id="rId41"/>
     <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
